--- a/docs/19_fcl_sample_loan_raw_dump.xlsx
+++ b/docs/19_fcl_sample_loan_raw_dump.xlsx
@@ -128,7 +128,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="21">
+  <fills count="22">
     <fill>
       <patternFill/>
     </fill>
@@ -230,6 +230,11 @@
         <fgColor rgb="00F2E6EF"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF8E1"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="6">
     <border>
@@ -301,7 +306,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="49">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -441,6 +446,9 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="21" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1006,7 +1014,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M25"/>
+  <dimension ref="A1:M26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -2559,8 +2567,16 @@
       </c>
       <c r="M25" s="6" t="inlineStr"/>
     </row>
+    <row r="26" ht="64" customHeight="1">
+      <c r="A26" s="49" t="inlineStr">
+        <is>
+          <t>code 列说明（rule 在 PrefectFlow 代码中的出处）： pool = ETL 建表/SQL 代码 flow/basic_data/basic_data_config/basic_data_pool_config.py（在 Redshift 建 FCL 各表、跑 SQL 规则）； asset = BPS 同步 SQL 代码 flow/bps/bps_config/asset_managment_config.py（把 Redshift 结果同步进 BPS 表）； view = BPS 视图 biz_data_view_loan_details_foreclosure 的定义（SHOW CREATE VIEW）； 冒号后数字 = 该文件的行号（例 pool:273 = 该文件第 273 行；GitLab commit 钉 32a750a3，可点开对应行）。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="2">
+    <mergeCell ref="A26:M26"/>
     <mergeCell ref="A1:M1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/19_fcl_sample_loan_raw_dump.xlsx
+++ b/docs/19_fcl_sample_loan_raw_dump.xlsx
@@ -1014,7 +1014,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M26"/>
+  <dimension ref="A1:M27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1172,110 +1172,114 @@
     <row r="4" ht="96" customHeight="1">
       <c r="A4" s="16" t="inlineStr">
         <is>
-          <t>③ newrez.portnewrezbk</t>
+          <t>②c carrington.portcarrington</t>
         </is>
       </c>
       <c r="B4" s="16" t="inlineStr">
         <is>
-          <t>L1 源（Newrez 破产源）</t>
+          <t>L1 源（Carrington FCL 主源）</t>
         </is>
       </c>
       <c r="C4" s="16" t="inlineStr">
         <is>
-          <t>Newrez 破产(BK)源表，按贷款×破产申请记录，含 bkstatus/bkchapter/bkfileddate 等编码字段。</t>
+          <t>Carrington 每日推送的法拍(FCL)主源表（共 199 列，本工作簿只渲染 pipeline 实际消费的 9 列）——含 fcl_flag(活跃标志)、fcl_sub_status(子状态)、fcl_referral_date(转律日)、fcl_scheduled_sale_date/fcl_sale_held_date(拍卖日)、fcl_attorney_name(律所)、carrington_ln(Carr 自有号)。</t>
         </is>
       </c>
       <c r="D4" s="16" t="inlineStr">
         <is>
-          <t>BK 事实底座；为 FCL 提供‘是否在破产保护(暂停法拍)’的判断。</t>
+          <t>Carrington 一家的法拍原始事实底座；与 Newrez/Capecodfive 并列，在 L4 CREATE_BASIC_FCL 经 UNION 汇入统一 FCL 事实表。</t>
         </is>
       </c>
       <c r="E4" s="16" t="inlineStr">
         <is>
-          <t>破产支线起点（L1）：BK 原始落库，为 FCL 提供「是否在破产保护、需暂停法拍」的判断起点。</t>
+          <t>源保真底座（L1，Carrington 分支）：Carr 字段名/口径与 Newrez 不同，先原样落地，再到 ⑨ UNION 时改名/计算对齐（如 activefcflag=CASE fcl_flag='Active'、fcstage=fcl_sub_status）。</t>
         </is>
       </c>
       <c r="F4" s="16" t="inlineStr">
         <is>
-          <t>破产是法拍的暂停因素，需单列保真；编码值经 datadic 解码成业务文案。</t>
+          <t>各 Servicer 文件格式不同，先‘一家一张原始表’保真，再 L4 统一 UNION，便于回溯对账。</t>
         </is>
       </c>
       <c r="G4" s="16" t="inlineStr">
         <is>
-          <t>查某贷款原始破产章节/状态/申请日，或核对 BPS 破产面板。</t>
+          <t>想看某 Carrington 贷款的原始 FCL 取值，或核对 ⑨ 的 Carr 派生字段是否忠实于此源时。</t>
         </is>
       </c>
       <c r="H4" s="16" t="inlineStr">
         <is>
-          <t>1 行/贷款/破产申请(bkfileddate)；多次申请多行。</t>
+          <t>1 行/贷款/snap_shot_date（每日快照）；本 dump 取 snap_shot_date=2026-06-10。</t>
         </is>
       </c>
       <c r="I4" s="16" t="inlineStr">
         <is>
-          <t>Servicer 文件(S3, L0) → newrez.portnewrezbk</t>
+          <t>Servicer 文件(Carrington, L0) → carrington.portcarrington</t>
         </is>
       </c>
       <c r="J4" s="16" t="inlineStr">
         <is>
-          <t>Servicer 文件(S3, L0)</t>
+          <t>Servicer 文件(Carrington, L0)</t>
         </is>
       </c>
       <c r="K4" s="16" t="inlineStr">
         <is>
-          <t>portnewrezbk → port.basic_data_loan_foreclosure_bankruptcy〔解码 bkstatus，basic_data_pool_config.py:331-370，JOIN newrez.portnewrezdatadic〕 → bpms.sync_loan_foreclosure_bankruptcy〔asset_managment_config.py:822-843〕 → bpms.biz_data_view_loan_details_foreclosure(视图) → BPS 破产面板</t>
+          <t>portcarrington → tempfc.temp_basic_data_fcl(CREATE_BASIC_FCL Carrington UNION 分支，pool:1574-1611) → port.basic_data_loan_fcl(全 servicer UNION) → { port.basic_data_loan_foreclosure / port.fcl_stage_info / ... } → bpms.sync_* → bpms.biz_data_view_loan_details_foreclosure → BPS 法拍面板。另：Carrington 分支 → port.basic_data_fcl_related(⑫，CREATE_FCL_RELATE_ATTR pool:1745-1770)</t>
         </is>
       </c>
       <c r="L4" s="16" t="inlineStr">
         <is>
-          <t>port.basic_data_loan_foreclosure_bankruptcy、bpms.sync_loan_foreclosure_bankruptcy、bpms.biz_data_view_loan_details_foreclosure</t>
-        </is>
-      </c>
-      <c r="M4" s="16" t="inlineStr"/>
+          <t>tempfc.temp_basic_data_fcl、port.basic_data_loan_fcl、port.basic_data_loan_foreclosure、port.basic_data_fcl_related、bpms.sync_loan_foreclosure、bpms.biz_data_view_loan_details_foreclosure</t>
+        </is>
+      </c>
+      <c r="M4" s="16" t="inlineStr">
+        <is>
+          <t>圈号 ②c 为【正式·可扩展】编号。★②家族编号法（为后续不断新增 servicer 设计）：② = Newrez portnewrezfc（primary/canonical，与 doc 19/25 既有 ② 一致）；此后每新增一个 servicer 的 FCL L1 源 = 『②+servicer 小写后缀』——②c=Carrington、②cc=Capecodfive（未来纳入时）、②sl=SLS、②se=Selene、②mr=MRC、②av=Arvest、②fci=FCI…依此类推。如此 ③…㉔ 全局序号【永不位移】（doc 19/25 等对 ②-㉔ 已有上万处引用，插号会大规模破坏），且 servicer 源可无限扩展、同族一眼可辨（都挂在 ② 下）。Capecodfive 源(portcapecodfive_monthly_collections)同为 L1 servicer 源但暂未纳入（不进 bpms 主表、当前无样本贷款）；纳入时即用 ②cc。</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="96" customHeight="1">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>④ newrez.portnewrezlm</t>
+          <t>③ newrez.portnewrezbk</t>
         </is>
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>L1 源（Newrez 损失缓解 LM 源）</t>
+          <t>L1 源（Newrez 破产源）</t>
         </is>
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>Newrez 损失缓解(LM)源表，按贷款×LM 周期(dealstartdate)，含 lmdeal/lmprogram/lmstatus/lmdecision 等编码。</t>
+          <t>Newrez 破产(BK)源表，按贷款×破产申请记录，含 bkstatus/bkchapter/bkfileddate 等编码字段。</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>LM 事实底座；提供‘是否在协商还款方案(暂停/替代法拍)’。</t>
+          <t>BK 事实底座；为 FCL 提供‘是否在破产保护(暂停法拍)’的判断。</t>
         </is>
       </c>
       <c r="E5" s="6" t="inlineStr">
         <is>
-          <t>LM 支线起点（L1）：损失缓解原始落库，为 FCL 提供「协商还款方案、暂停/替代法拍」的判断起点。</t>
+          <t>破产支线起点（L1）：BK 原始落库，为 FCL 提供「是否在破产保护、需暂停法拍」的判断起点。</t>
         </is>
       </c>
       <c r="F5" s="6" t="inlineStr">
         <is>
-          <t>LM 是法拍的替代/暂停路径，需单列保真；编码经 datadic 解码。</t>
+          <t>破产是法拍的暂停因素，需单列保真；编码值经 datadic 解码成业务文案。</t>
         </is>
       </c>
       <c r="G5" s="6" t="inlineStr">
         <is>
-          <t>查某贷款 LM 周期/项目/决定原值，或核对 BPS LM 面板。</t>
+          <t>查某贷款原始破产章节/状态/申请日，或核对 BPS 破产面板。</t>
         </is>
       </c>
       <c r="H5" s="6" t="inlineStr">
         <is>
-          <t>1 行/贷款/LM 周期(dealstartdate)；多周期多行。</t>
+          <t>1 行/贷款/破产申请(bkfileddate)；多次申请多行。</t>
         </is>
       </c>
       <c r="I5" s="6" t="inlineStr">
         <is>
-          <t>Servicer 文件(S3, L0) → newrez.portnewrezlm</t>
+          <t>Servicer 文件(S3, L0) → newrez.portnewrezbk</t>
         </is>
       </c>
       <c r="J5" s="6" t="inlineStr">
@@ -1285,12 +1289,12 @@
       </c>
       <c r="K5" s="6" t="inlineStr">
         <is>
-          <t>portnewrezlm → port.basic_data_loan_foreclosure_loss_mitigation〔basic_data_pool_config.py:799-843，JOIN newrez.portnewrezdatadic〕 → bpms.sync_loan_foreclosure_loss_mitigation〔asset_managment_config.py:799-819〕 → bpms.biz_data_view_loan_details_foreclosure(视图) → BPS LM 面板</t>
+          <t>portnewrezbk → port.basic_data_loan_foreclosure_bankruptcy〔解码 bkstatus，basic_data_pool_config.py:331-370，JOIN newrez.portnewrezdatadic〕 → bpms.sync_loan_foreclosure_bankruptcy〔asset_managment_config.py:822-843〕 → bpms.biz_data_view_loan_details_foreclosure(视图) → BPS 破产面板。另：bk.activebkflag → port.basic_data_fcl_related.bk_flag(⑫，CREATE_FCL_RELATE_ATTR pool:1720)</t>
         </is>
       </c>
       <c r="L5" s="6" t="inlineStr">
         <is>
-          <t>port.basic_data_loan_foreclosure_loss_mitigation、bpms.sync_loan_foreclosure_loss_mitigation、bpms.biz_data_view_loan_details_foreclosure</t>
+          <t>port.basic_data_loan_foreclosure_bankruptcy、port.basic_data_fcl_related、bpms.sync_loan_foreclosure_bankruptcy、bpms.biz_data_view_loan_details_foreclosure</t>
         </is>
       </c>
       <c r="M5" s="6" t="inlineStr"/>
@@ -1298,47 +1302,47 @@
     <row r="6" ht="96" customHeight="1">
       <c r="A6" s="16" t="inlineStr">
         <is>
-          <t>⑤ newrez.portnewrezgeneral</t>
+          <t>④ newrez.portnewrezlm</t>
         </is>
       </c>
       <c r="B6" s="16" t="inlineStr">
         <is>
-          <t>L1 源（Newrez 通用源）</t>
+          <t>L1 源（Newrez 损失缓解 LM 源）</t>
         </is>
       </c>
       <c r="C6" s="16" t="inlineStr">
         <is>
-          <t>Newrez 通用源表(125 列)，含 legalstatus、delinquency_status_mba(MBA 逾期分类)、nextduedate 等账户层属性。</t>
+          <t>Newrez 损失缓解(LM)源表，按贷款×LM 周期(dealstartdate)，含 lmdeal/lmprogram/lmstatus/lmdecision 等编码。</t>
         </is>
       </c>
       <c r="D6" s="16" t="inlineStr">
         <is>
-          <t>逾期(delinquency)支线的源头；提供 delq_status 原值。</t>
+          <t>LM 事实底座；提供‘是否在协商还款方案(暂停/替代法拍)’。</t>
         </is>
       </c>
       <c r="E6" s="16" t="inlineStr">
         <is>
-          <t>逾期支线起点（L1）：提供 delq_status 等账户原值，喂入 L2 逾期统一日表。</t>
+          <t>LM 支线起点（L1）：损失缓解原始落库，为 FCL 提供「协商还款方案、暂停/替代法拍」的判断起点。</t>
         </is>
       </c>
       <c r="F6" s="16" t="inlineStr">
         <is>
-          <t>逾期与 FCL 是两条支线——逾期来自 general 表经 days360 归一，FCL 来自 portnewrezfc 显式标志；二者在 L4 汇合。FCL 码绝不由 days360 推导。</t>
+          <t>LM 是法拍的替代/暂停路径，需单列保真；编码经 datadic 解码。</t>
         </is>
       </c>
       <c r="G6" s="16" t="inlineStr">
         <is>
-          <t>查某贷款原始逾期分类/法律状态/下次到期日。</t>
+          <t>查某贷款 LM 周期/项目/决定原值，或核对 BPS LM 面板。</t>
         </is>
       </c>
       <c r="H6" s="16" t="inlineStr">
         <is>
-          <t>1 行/贷款/dataasof。</t>
+          <t>1 行/贷款/LM 周期(dealstartdate)；多周期多行。</t>
         </is>
       </c>
       <c r="I6" s="16" t="inlineStr">
         <is>
-          <t>Servicer 文件(S3, L0) → newrez.portnewrezgeneral</t>
+          <t>Servicer 文件(S3, L0) → newrez.portnewrezlm</t>
         </is>
       </c>
       <c r="J6" s="16" t="inlineStr">
@@ -1348,12 +1352,12 @@
       </c>
       <c r="K6" s="16" t="inlineStr">
         <is>
-          <t>portnewrezgeneral.delinquency_status_mba → port.portdaily_v2〔portdaily_config.py〕 → port.basic_data_daily_loan_common.delq_status(逾期支线 L2，daily_data_loan_common_config.py) → port.basic_data_daily_loan_common_clean.delinq(L3，daily_data_loan_common_clean_config.py，CASE+days360) → { port.basic_data_fcl_related.delq_status / port.fcl_stage_info.group / port.portmonthbase } → BPS</t>
+          <t>portnewrezlm → port.basic_data_loan_foreclosure_loss_mitigation〔basic_data_pool_config.py:799-843，JOIN newrez.portnewrezdatadic〕 → bpms.sync_loan_foreclosure_loss_mitigation〔asset_managment_config.py:799-819〕 → bpms.biz_data_view_loan_details_foreclosure(视图) → BPS LM 面板</t>
         </is>
       </c>
       <c r="L6" s="16" t="inlineStr">
         <is>
-          <t>port.portdaily_v2、port.basic_data_daily_loan_common、port.basic_data_daily_loan_common_clean、port.basic_data_fcl_related、port.fcl_stage_info、port.portmonthbase、bpms.sync_fcl_stage_info</t>
+          <t>port.basic_data_loan_foreclosure_loss_mitigation、bpms.sync_loan_foreclosure_loss_mitigation、bpms.biz_data_view_loan_details_foreclosure</t>
         </is>
       </c>
       <c r="M6" s="16" t="inlineStr"/>
@@ -1361,37 +1365,37 @@
     <row r="7" ht="96" customHeight="1">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>⑥ newrez.portnewrezprop</t>
+          <t>⑤ newrez.portnewrezgeneral</t>
         </is>
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>L1 源（Newrez 房产源）</t>
+          <t>L1 源（Newrez 通用源）</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>Newrez 房产源表(32 列)，含 propertystate(州，定司法/非司法)、LTV、occupancy 等。</t>
+          <t>Newrez 通用源表(125 列)，含 legalstatus、delinquency_status_mba(MBA 逾期分类)、nextduedate 等账户层属性。</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>提供物业/州属性；州决定 FCL 走司法(judicial)还是非司法路径。</t>
+          <t>逾期(delinquency)支线的源头；提供 delq_status 原值。</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr">
         <is>
-          <t>维度源（L1）：提供物业州等属性，决定 FCL 走司法/非司法路径与时长口径。</t>
+          <t>逾期支线起点（L1）：提供 delq_status 等账户原值，喂入 L2 逾期统一日表。</t>
         </is>
       </c>
       <c r="F7" s="6" t="inlineStr">
         <is>
-          <t>司法/非司法影响 FCL 时长与阶段口径，需物业州维度（实测 state 取自 portnewrezprop.propertystate）。</t>
+          <t>逾期与 FCL 是两条支线——逾期来自 general 表经 days360 归一，FCL 来自 portnewrezfc 显式标志；二者在 L4 汇合。FCL 码绝不由 days360 推导。</t>
         </is>
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>查某贷款物业州/LTV/占用情况。</t>
+          <t>查某贷款原始逾期分类/法律状态/下次到期日。</t>
         </is>
       </c>
       <c r="H7" s="6" t="inlineStr">
@@ -1401,7 +1405,7 @@
       </c>
       <c r="I7" s="6" t="inlineStr">
         <is>
-          <t>Servicer 文件(S3, L0) → newrez.portnewrezprop</t>
+          <t>Servicer 文件(S3, L0) → newrez.portnewrezgeneral</t>
         </is>
       </c>
       <c r="J7" s="6" t="inlineStr">
@@ -1411,12 +1415,12 @@
       </c>
       <c r="K7" s="6" t="inlineStr">
         <is>
-          <t>portnewrezprop.propertystate → port.basic_data_daily_loan_common(州维度) / port.basic_data_loan_foreclosure(summary_judicial_foreclosure 司法标志) → bpms.sync_loan_foreclosure → BPS</t>
+          <t>portnewrezgeneral.delinquency_status_mba 有两条独立去向：(A 逾期支线) → port.portdaily_v2 → port.basic_data_daily_loan_common.delq_status(L2) → port.basic_data_daily_loan_common_clean.delinq(L3，CASE+days360) → port.portmonthbase → BPS；(B FCL 分组) general 被 CREATE_FCL_RELATE_ATTR(pool:1696-1770) 直接读取 → port.basic_data_fcl_related.delq_status → port.fcl_stage_info.group → bpms.sync_fcl_stage_info → BPS。⚠️ B 路不经 daily_loan_common_clean——⑫ 用同一 CASE+days360 逻辑独立重算。</t>
         </is>
       </c>
       <c r="L7" s="6" t="inlineStr">
         <is>
-          <t>port.basic_data_daily_loan_common、port.basic_data_loan_foreclosure、bpms.sync_loan_foreclosure</t>
+          <t>port.portdaily_v2、port.basic_data_daily_loan_common、port.basic_data_daily_loan_common_clean、port.basic_data_fcl_related、port.fcl_stage_info、port.portmonthbase、bpms.sync_fcl_stage_info</t>
         </is>
       </c>
       <c r="M7" s="6" t="inlineStr"/>
@@ -1424,259 +1428,259 @@
     <row r="8" ht="96" customHeight="1">
       <c r="A8" s="16" t="inlineStr">
         <is>
-          <t>⑦ port.basic_data_daily_loan_common</t>
+          <t>⑥ newrez.portnewrezprop</t>
         </is>
       </c>
       <c r="B8" s="16" t="inlineStr">
         <is>
-          <t>L2 逾期支线 统一日表（Redshift）</t>
+          <t>L1 源（Newrez 房产源）</t>
         </is>
       </c>
       <c r="C8" s="16" t="inlineStr">
         <is>
-          <t>逾期支线 L2 统一日表(78 列)——全 servicer UNION 后的标准日表，含 delq_status、fcl_flag、lm_flag 等(asofdate)。</t>
+          <t>Newrez 房产源表(32 列)，含 propertystate(州，定司法/非司法)、LTV、occupancy 等。</t>
         </is>
       </c>
       <c r="D8" s="16" t="inlineStr">
         <is>
-          <t>逾期/状态归一的统一入口；L3 清洗的上游。</t>
+          <t>提供物业/州属性；州决定 FCL 走司法(judicial)还是非司法路径。</t>
         </is>
       </c>
       <c r="E8" s="16" t="inlineStr">
         <is>
-          <t>逾期支线归一入口（L2）：全 servicer UNION 成统一日表，承接各家差异，喂 L3 清洗。</t>
+          <t>维度源（L1）：提供物业州等属性，决定 FCL 走司法/非司法路径与时长口径。</t>
         </is>
       </c>
       <c r="F8" s="16" t="inlineStr">
         <is>
-          <t>各家逾期/状态字段名与取值不同，先 UNION 成统一日表；注意 fcl_flag 在此并未真正归一(Newrez/SLS 为 NULL)，真正归一在 L4 FCL 业务族。</t>
+          <t>司法/非司法影响 FCL 时长与阶段口径，需物业州维度（实测 state 取自 portnewrezprop.propertystate）。</t>
         </is>
       </c>
       <c r="G8" s="16" t="inlineStr">
         <is>
-          <t>查‘统一后的每日逾期/状态原值’、对账各家归一。</t>
+          <t>查某贷款物业州/LTV/占用情况。</t>
         </is>
       </c>
       <c r="H8" s="16" t="inlineStr">
         <is>
-          <t>1 行/贷款/asofdate。</t>
+          <t>1 行/贷款/dataasof。</t>
         </is>
       </c>
       <c r="I8" s="16" t="inlineStr">
         <is>
-          <t>Servicer 文件(L0) → newrez.portnewrezgeneral(等各家) → port.portdaily_v2〔portdaily_config.py〕 → port.basic_data_daily_loan_common〔daily_data_loan_common_config.py〕</t>
+          <t>Servicer 文件(S3, L0) → newrez.portnewrezprop</t>
         </is>
       </c>
       <c r="J8" s="16" t="inlineStr">
         <is>
-          <t>Servicer 文件(L0)、newrez.portnewrezgeneral、newrez.portnewrezfc、port.portdaily_v2</t>
+          <t>Servicer 文件(S3, L0)</t>
         </is>
       </c>
       <c r="K8" s="16" t="inlineStr">
         <is>
-          <t>→ port.basic_data_daily_loan_common_clean(L3) → { port.portmonthbase / port.basic_data_fcl_related.delq_status / port.fcl_stage_info.group } → BPS</t>
+          <t>portnewrezprop.propertystate → port.basic_data_daily_loan_common(州维度) / port.basic_data_loan_foreclosure(summary_judicial_foreclosure 司法标志) → bpms.sync_loan_foreclosure → BPS。另：pr.propertystate → port.basic_data_fcl_related.propertystate(⑫，CREATE_FCL_RELATE_ATTR pool:1721)</t>
         </is>
       </c>
       <c r="L8" s="16" t="inlineStr">
         <is>
-          <t>port.basic_data_daily_loan_common_clean、port.basic_data_fcl_related、port.fcl_stage_info、port.portmonthbase</t>
-        </is>
-      </c>
-      <c r="M8" s="16" t="inlineStr">
-        <is>
-          <t>fcl_flag 在 L2 未归一（直传，Newrez/SLS NULL）；真正归一在 L4 FCL 业务族。</t>
-        </is>
-      </c>
+          <t>port.basic_data_daily_loan_common、port.basic_data_loan_foreclosure、port.basic_data_fcl_related、bpms.sync_loan_foreclosure</t>
+        </is>
+      </c>
+      <c r="M8" s="16" t="inlineStr"/>
     </row>
     <row r="9" ht="96" customHeight="1">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t>⑧ port.basic_data_daily_loan_common_clean</t>
+          <t>⑦ port.basic_data_daily_loan_common</t>
         </is>
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>L3 逾期支线 清洗日表（Redshift）</t>
+          <t>L2 逾期支线 统一日表（Redshift）</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>逾期支线 L3 清洗日表(103 列)——把 delq_status 经 CASE 归一成标准 delinq 码(C/D30/D60/D90/D120P/FCL/REO/P)，并用 days360(nextduedate,fctrdt) 分桶(fctrdt)。</t>
+          <t>逾期支线 L2 统一日表(78 列)——全 servicer UNION 后的标准日表，含 delq_status、fcl_flag、lm_flag 等(asofdate)。</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>标准逾期码的单一来源；喂 portmonthbase 与 FCL 业务族(stage 分组)。</t>
+          <t>逾期/状态归一的统一入口；L3 清洗的上游。</t>
         </is>
       </c>
       <c r="E9" s="6" t="inlineStr">
         <is>
-          <t>标准逾期码单一来源（L3）：CASE+days360 把 delq_status 归一为标准 delinq 码，喂 portmonthbase 与 FCL stage 分组。</t>
+          <t>逾期支线归一入口（L2）：全 servicer UNION 成统一日表，承接各家差异，喂 L3 清洗。</t>
         </is>
       </c>
       <c r="F9" s="6" t="inlineStr">
         <is>
-          <t>业务要统一的 MBA 逾期码；文本状态(Foreclosure*/REO/Paid*)直接映射，其余按 days360 天数分桶。注意：FCL 码只来自 servicer 显式法拍状态，绝不由 days360 推导。</t>
+          <t>各家逾期/状态字段名与取值不同，先 UNION 成统一日表；注意 fcl_flag 在此并未真正归一(Newrez/SLS 为 NULL)，真正归一在 L4 FCL 业务族。</t>
         </is>
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>查‘标准化后的逾期码/天数桶口径’、核对 days360 计算。</t>
+          <t>查‘统一后的每日逾期/状态原值’、对账各家归一。</t>
         </is>
       </c>
       <c r="H9" s="6" t="inlineStr">
         <is>
-          <t>1 行/贷款/fctrdt。</t>
+          <t>1 行/贷款/asofdate。</t>
         </is>
       </c>
       <c r="I9" s="6" t="inlineStr">
         <is>
-          <t>… → port.basic_data_daily_loan_common → port.basic_data_daily_loan_common_clean〔daily_data_loan_common_clean_config.py，CASE + days360〕</t>
+          <t>Servicer 文件(L0) → newrez.portnewrezgeneral(等各家) → port.portdaily_v2〔portdaily_config.py〕 → port.basic_data_daily_loan_common〔daily_data_loan_common_config.py〕</t>
         </is>
       </c>
       <c r="J9" s="6" t="inlineStr">
         <is>
-          <t>port.basic_data_daily_loan_common、port.portdaily_v2、newrez.portnewrezgeneral</t>
+          <t>Servicer 文件(L0)、newrez.portnewrezgeneral、newrez.portnewrezfc、port.portdaily_v2</t>
         </is>
       </c>
       <c r="K9" s="6" t="inlineStr">
         <is>
-          <t>→ { port.portmonthbase / port.basic_data_fcl_related.delq_status / port.fcl_stage_info.group } → BPS。另：旁支 port.basic_data_loan_delinq_clean(含 is_ghost_payoff 等)实测存在，但其生成代码不在 PrefectFlow 仓库(grep 0 命中，开放问题)。</t>
+          <t>→ port.basic_data_daily_loan_common_clean(L3) → port.portmonthbase → BPS（逾期支线月度路径）。注：FCL 分组 fcl_stage_info.group / ⑫ basic_data_fcl_related.delq_status 不经本表——⑫ 由 Newrez 原始表(g.delinquency_status_mba + days360(pmt.nextduedate)) 独立重算同一逻辑，见 CREATE_FCL_RELATE_ATTR pool:1696-1770。</t>
         </is>
       </c>
       <c r="L9" s="6" t="inlineStr">
         <is>
-          <t>port.basic_data_fcl_related、port.fcl_stage_info、port.portmonthbase</t>
+          <t>port.basic_data_daily_loan_common_clean、port.portmonthbase</t>
         </is>
       </c>
       <c r="M9" s="6" t="inlineStr">
         <is>
-          <t>旁支 port.basic_data_loan_delinq_clean 生成代码不在仓库（grep 0 命中，开放问题），未列为确定下游。</t>
+          <t>fcl_flag 在 L2 未归一（直传，Newrez/SLS NULL）；真正归一在 L4 FCL 业务族。逾期支线(本表/⑧)只流向 portmonthbase 月度，不流向 ⑫/⑬ 的 FCL 分组（后者独立重算，2026-06-15 Code-First 订正）。</t>
         </is>
       </c>
     </row>
     <row r="10" ht="96" customHeight="1">
       <c r="A10" s="16" t="inlineStr">
         <is>
-          <t>⑨ tempfc.temp_basic_data_fcl</t>
+          <t>⑧ port.basic_data_daily_loan_common_clean</t>
         </is>
       </c>
       <c r="B10" s="16" t="inlineStr">
         <is>
-          <t>L4 改名临时表（Redshift 运行时中间产物）</t>
+          <t>L3 逾期支线 清洗日表（Redshift）</t>
         </is>
       </c>
       <c r="C10" s="16" t="inlineStr">
         <is>
-          <t>Redshift 运行时改名临时表(37 列)——把各 servicer 原始列(如 fcreferraldate)改成统一列(referral_start_date)的中间产物。</t>
+          <t>逾期支线 L3 清洗日表(103 列)——把 delq_status 经 CASE 归一成标准 delinq 码(C/D30/D60/D90/D120P/FCL/REO/P)，并用 days360(nextduedate,fctrdt) 分桶(fctrdt)。</t>
         </is>
       </c>
       <c r="D10" s="16" t="inlineStr">
         <is>
-          <t>port.basic_data_loan_fcl 的直接上游；承接‘改名’这一步。</t>
+          <t>逾期支线标准逾期码的单一来源；喂 port.portmonthbase 月度（不喂 FCL 分组——见下游说明）。</t>
         </is>
       </c>
       <c r="E10" s="16" t="inlineStr">
         <is>
-          <t>列名统一中间产物（L4）：承接「改名」这一步，连接 L1 各家源与 L4 UNION 事实表。</t>
+          <t>标准逾期码单一来源（L3，逾期支线）：CASE+days360 把 delq_status 归一为标准 delinq 码，喂 port.portmonthbase。</t>
         </is>
       </c>
       <c r="F10" s="16" t="inlineStr">
         <is>
-          <t>UNION 前必须先统一列名；单列一张临时表做改名，逻辑清晰、便于调试；运行时产物。</t>
+          <t>业务要统一的 MBA 逾期码；文本状态(Foreclosure*/REO/Paid*)直接映射，其余按 days360 天数分桶。注意：FCL 码只来自 servicer 显式法拍状态，绝不由 days360 推导。</t>
         </is>
       </c>
       <c r="G10" s="16" t="inlineStr">
         <is>
-          <t>排查‘统一列名 ↔ 源列名’映射、定位改名是否正确。</t>
+          <t>查‘标准化后的逾期码/天数桶口径’、核对 days360 计算。</t>
         </is>
       </c>
       <c r="H10" s="16" t="inlineStr">
         <is>
-          <t>1 行/贷款/dataasof。</t>
+          <t>1 行/贷款/fctrdt。</t>
         </is>
       </c>
       <c r="I10" s="16" t="inlineStr">
         <is>
-          <t>newrez.portnewrezfc(各家源) → tempfc.temp_basic_data_fcl〔改名 basic_data_pool_config.py ~:1538-1565〕</t>
+          <t>… → port.basic_data_daily_loan_common → port.basic_data_daily_loan_common_clean〔daily_data_loan_common_clean_config.py，CASE + days360〕</t>
         </is>
       </c>
       <c r="J10" s="16" t="inlineStr">
         <is>
-          <t>newrez.portnewrezfc、Servicer 文件(L0)</t>
+          <t>port.basic_data_daily_loan_common、port.portdaily_v2、newrez.portnewrezgeneral</t>
         </is>
       </c>
       <c r="K10" s="16" t="inlineStr">
         <is>
-          <t>→ port.basic_data_loan_fcl(UNION) → FCL 业务族(foreclosure/stage/hold/lm/bk) → bpms.sync_* → BPS</t>
+          <t>→ port.portmonthbase → BPS（逾期支线月度路径）。⚠️ 本 L3 清洗层不流向 FCL 分组：⑫ basic_data_fcl_related.delq_status / ⑬ fcl_stage_info.group 由 Newrez 原始表(g.delinquency_status_mba + days360(pmt.nextduedate)) 独立重算同一 CASE+days360 逻辑(CREATE_FCL_RELATE_ATTR pool:1696-1770)，并不读本表(2026-06-15 Code-First 订正)。另：旁支 port.basic_data_loan_delinq_clean(含 is_ghost_payoff 等)实测存在，但其生成代码不在 PrefectFlow 仓库(grep 0 命中，开放问题)。</t>
         </is>
       </c>
       <c r="L10" s="16" t="inlineStr">
         <is>
-          <t>port.basic_data_loan_fcl、port.basic_data_loan_foreclosure、port.fcl_stage_info、port.basic_data_loan_foreclosure_hold、port.basic_data_loan_foreclosure_loss_mitigation、port.basic_data_loan_foreclosure_bankruptcy</t>
-        </is>
-      </c>
-      <c r="M10" s="16" t="inlineStr"/>
+          <t>port.portmonthbase</t>
+        </is>
+      </c>
+      <c r="M10" s="16" t="inlineStr">
+        <is>
+          <t>旁支 port.basic_data_loan_delinq_clean 生成代码不在仓库（grep 0 命中，开放问题），未列为确定下游。逾期支线 L3 不喂 ⑫/⑬ 的 FCL 分组（后者独立重算同一逻辑，2026-06-15 Code-First 订正）。</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="96" customHeight="1">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>⑩ port.basic_data_loan_fcl</t>
+          <t>⑨ tempfc.temp_basic_data_fcl</t>
         </is>
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>L4 FCL 事实表（Redshift 快照中间）</t>
+          <t>L4 改名临时表（Redshift 运行时中间产物）</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>Redshift FCL 事实表——portnewrezfc 等经改名后 UNION 全 6 家 servicer 的统一列宽表(每贷款最新 dataasof)。</t>
+          <t>Redshift 运行时改名临时表(37 列)——把各 servicer 原始列(如 fcreferraldate)改成统一列(referral_start_date)的中间产物。</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>FCL 计算的统一入口；屏蔽各 servicer 列名差异。</t>
+          <t>port.basic_data_loan_fcl 的直接上游；承接‘改名’这一步。</t>
         </is>
       </c>
       <c r="E11" s="6" t="inlineStr">
         <is>
-          <t>全 servicer UNION 事实入口（L4）：屏蔽各家列名差异，作为所有 FCL 业务子表的共同上游。</t>
+          <t>列名统一中间产物（L4）：承接「改名」这一步，连接 L1 各家源与 L4 UNION 事实表。</t>
         </is>
       </c>
       <c r="F11" s="6" t="inlineStr">
         <is>
-          <t>各家列名不同，先改名(tempfc.temp_basic_data_fcl)再 UNION 成一张统一事实表，下游只面对一套列名。</t>
+          <t>为什么单列这张临时表、而非直接生成 ⑩：它是【单消费者暂存表】(仅被 ⑩ 读，pool:1686)，物化它是工程权衡而非复用——①关注点分离：⑨ 专做‘三家 servicer 异构源 UNION + 列名归一化’(pool:1532-1654)，⑩ 只做‘LEFT JOIN Hold 历史’(pool:1657-1692)；②可读：单 UNION 约 120 行，内联进 ⑩ 的 join 会变成约 150 行嵌套大查询；③Redshift 性能：先把 UNION 物化成带统计信息的实体表再 join，比‘join 里塞三路 UNION 子查询’计划更稳、更快；④可调试：可直接查暂存表看‘UNION 完、挂 Hold 前’的中间态。属标准 ETL staging、非缺陷；理论上可用 CTE/真 TEMP 表省一次落盘，但当前复杂度下拆两步更优。</t>
         </is>
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>查‘统一列名后的 FCL 字段值’，或定位某下游字段来自哪根统一列。</t>
+          <t>排查‘统一列名 ↔ 源列名’映射、定位改名是否正确。</t>
         </is>
       </c>
       <c r="H11" s="6" t="inlineStr">
         <is>
-          <t>1 行/贷款（每贷款最新 dataasof）。</t>
+          <t>1 行/贷款/dataasof。</t>
         </is>
       </c>
       <c r="I11" s="6" t="inlineStr">
         <is>
-          <t>Servicer 文件(L0) → newrez.portnewrezfc(+各家对应表) → tempfc.temp_basic_data_fcl(改名) → port.basic_data_loan_fcl〔UNION，basic_data_pool_config.py〕</t>
+          <t>newrez.portnewrezfc(各家源) → tempfc.temp_basic_data_fcl〔改名 basic_data_pool_config.py ~:1538-1565〕</t>
         </is>
       </c>
       <c r="J11" s="6" t="inlineStr">
         <is>
-          <t>Servicer 文件(L0)、newrez.portnewrezfc、(sls/carrington/mrc/fci/selene 对应源表)、tempfc.temp_basic_data_fcl</t>
+          <t>newrez.portnewrezfc、Servicer 文件(L0)</t>
         </is>
       </c>
       <c r="K11" s="6" t="inlineStr">
         <is>
-          <t>basic_data_loan_fcl → { port.basic_data_loan_foreclosure〔GEN_FCL_DETAIL :253-305〕 / port.fcl_stage_info〔GEN_FCL_STAGE :1774-2440〕 / port.basic_data_loan_foreclosure_hold〔:466-768〕 / port.basic_data_loan_foreclosure_loss_mitigation〔:799-843〕 / port.basic_data_loan_foreclosure_bankruptcy〔:331-370〕 } → bpms.sync_* → 视图 → BPS</t>
+          <t>→ port.basic_data_loan_fcl(UNION) → FCL 业务族(foreclosure/stage/hold/lm/bk) → bpms.sync_* → BPS</t>
         </is>
       </c>
       <c r="L11" s="6" t="inlineStr">
         <is>
-          <t>port.basic_data_loan_foreclosure、port.fcl_stage_info、port.basic_data_loan_foreclosure_hold、port.basic_data_loan_foreclosure_loss_mitigation、port.basic_data_loan_foreclosure_bankruptcy、bpms.sync_loan_foreclosure、bpms.sync_fcl_stage_info、bpms.sync_loan_foreclosure_hold、bpms.sync_loan_foreclosure_loss_mitigation、bpms.sync_loan_foreclosure_bankruptcy、bpms.biz_data_view_loan_details_foreclosure</t>
+          <t>port.basic_data_loan_fcl、port.basic_data_loan_foreclosure、port.fcl_stage_info、port.basic_data_loan_foreclosure_hold、port.basic_data_loan_foreclosure_loss_mitigation、port.basic_data_loan_foreclosure_bankruptcy</t>
         </is>
       </c>
       <c r="M11" s="6" t="inlineStr"/>
@@ -1684,62 +1688,62 @@
     <row r="12" ht="96" customHeight="1">
       <c r="A12" s="16" t="inlineStr">
         <is>
-          <t>⑪ port.basic_data_loan_foreclosure</t>
+          <t>⑩ port.basic_data_loan_fcl</t>
         </is>
       </c>
       <c r="B12" s="16" t="inlineStr">
         <is>
-          <t>L4 FCL 聚合（时间线，1 行/贷款）</t>
+          <t>L4 FCL 事实表（Redshift 快照中间）</t>
         </is>
       </c>
       <c r="C12" s="16" t="inlineStr">
         <is>
-          <t>Redshift FCL 聚合表(1 行/贷款)——一笔贷款端到端法拍时间线：各里程碑日期、当前状态(summary_foreclosure_status)、司法标志、在法拍天数(summary_days_in_fcl)。</t>
+          <t>Redshift FCL 事实表——portnewrezfc 等经改名后 UNION 全 6 家 servicer 的统一列宽表(每贷款最新 dataasof)。</t>
         </is>
       </c>
       <c r="D12" s="16" t="inlineStr">
         <is>
-          <t>bpms.sync_loan_foreclosure(BPS 主表)的直接上游；法拍主视图的数据底座。</t>
+          <t>FCL 计算的统一入口；屏蔽各 servicer 列名差异。</t>
         </is>
       </c>
       <c r="E12" s="16" t="inlineStr">
         <is>
-          <t>时间线收敛点（L4）：把散落里程碑/状态收敛成 1 行/贷款的可读时间线，作 BPS 主表直接上游。</t>
+          <t>全 servicer UNION 事实入口（L4）：屏蔽各家列名差异，作为所有 FCL 业务子表的共同上游。</t>
         </is>
       </c>
       <c r="F12" s="16" t="inlineStr">
         <is>
-          <t>把事实表里散落的里程碑/状态按业务规则(GEN_FCL_DETAIL CASE)收敛成 1 行/贷款的可读时间线；退出原因直接取 servicer 的 fcremovaldesc(无解码表)。</t>
+          <t>各家列名不同，先改名(tempfc.temp_basic_data_fcl)再 UNION 成一张统一事实表，下游只面对一套列名。</t>
         </is>
       </c>
       <c r="G12" s="16" t="inlineStr">
         <is>
-          <t>查某贷款法拍‘何时进入各里程碑/当前状态/在法拍多少天/为何退出’。</t>
+          <t>查‘统一列名后的 FCL 字段值’，或定位某下游字段来自哪根统一列。</t>
         </is>
       </c>
       <c r="H12" s="16" t="inlineStr">
         <is>
-          <t>1 行/贷款（含在途 + 已结）。</t>
+          <t>1 行/贷款（每贷款最新 dataasof）。</t>
         </is>
       </c>
       <c r="I12" s="16" t="inlineStr">
         <is>
-          <t>… → port.basic_data_loan_fcl → port.basic_data_loan_foreclosure〔GEN_FCL_DETAIL basic_data_pool_config.py:253-305；状态 CASE :273；司法 :277-279；在法拍天数 :1628〕</t>
+          <t>Servicer 文件(L0) → newrez.portnewrezfc(+各家对应表) → tempfc.temp_basic_data_fcl(改名) → port.basic_data_loan_fcl〔UNION，basic_data_pool_config.py〕</t>
         </is>
       </c>
       <c r="J12" s="16" t="inlineStr">
         <is>
-          <t>port.basic_data_loan_fcl、tempfc.temp_basic_data_fcl、newrez.portnewrezfc、Servicer 文件(L0)</t>
+          <t>Servicer 文件(L0)、newrez.portnewrezfc、(sls/carrington/mrc/fci/selene 对应源表)、tempfc.temp_basic_data_fcl</t>
         </is>
       </c>
       <c r="K12" s="16" t="inlineStr">
         <is>
-          <t>basic_data_loan_foreclosure → (Redshift→MySQL 同步 df_db_util.py:665-699 sync_to_mysql / 702-726 update_to_mysql) → bpms.sync_loan_foreclosure〔GEN_FORECLOSURE asset_managment_config.py:535-608；实时天数校正 :597-598〕 → bpms.biz_data_view_loan_details_foreclosure(视图) → BPS Summary/Timeline 面板</t>
+          <t>basic_data_loan_fcl → { port.basic_data_loan_foreclosure〔GEN_FCL_DETAIL :253-305〕 / port.fcl_stage_info〔GEN_FCL_STAGE :1774-2440〕 / port.basic_data_loan_foreclosure_hold〔:466-768〕 / port.basic_data_loan_foreclosure_loss_mitigation〔:799-843〕 / port.basic_data_loan_foreclosure_bankruptcy〔:331-370〕 } → bpms.sync_* → 视图 → BPS</t>
         </is>
       </c>
       <c r="L12" s="16" t="inlineStr">
         <is>
-          <t>bpms.sync_loan_foreclosure、bpms.biz_data_view_loan_details_foreclosure</t>
+          <t>port.basic_data_loan_foreclosure、port.fcl_stage_info、port.basic_data_loan_foreclosure_hold、port.basic_data_loan_foreclosure_loss_mitigation、port.basic_data_loan_foreclosure_bankruptcy、bpms.sync_loan_foreclosure、bpms.sync_fcl_stage_info、bpms.sync_loan_foreclosure_hold、bpms.sync_loan_foreclosure_loss_mitigation、bpms.sync_loan_foreclosure_bankruptcy、bpms.biz_data_view_loan_details_foreclosure</t>
         </is>
       </c>
       <c r="M12" s="16" t="inlineStr"/>
@@ -1747,62 +1751,62 @@
     <row r="13" ht="96" customHeight="1">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>⑫ port.basic_data_fcl_related</t>
+          <t>⑪ port.basic_data_loan_foreclosure</t>
         </is>
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>L4 FCL 关联/过滤中间表</t>
+          <t>L4 FCL 聚合（时间线，1 行/贷款）</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>FCL 关联属性中间表(14 列)——诉讼标志、清算类型、BK 标志、违约原因、delq_status 等。</t>
+          <t>Redshift FCL 聚合表(1 行/贷款)——一笔贷款端到端法拍时间线：各里程碑日期、当前状态(summary_foreclosure_status)、司法标志、在法拍天数(summary_days_in_fcl)。</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>给 stage 计算与过滤提供‘关联属性/分组键’(delq_status → stage group)。</t>
+          <t>bpms.sync_loan_foreclosure(BPS 主表)的直接上游；法拍主视图的数据底座。</t>
         </is>
       </c>
       <c r="E13" s="6" t="inlineStr">
         <is>
-          <t>分组键提供者（L4）：合并逾期码与 FCL 属性，为 stage 计算提供分组键（delq_status→group）。</t>
+          <t>时间线收敛点（L4）：把散落里程碑/状态收敛成 1 行/贷款的可读时间线，作 BPS 主表直接上游。</t>
         </is>
       </c>
       <c r="F13" s="6" t="inlineStr">
         <is>
-          <t>stage 计算需把逾期支线的 delq_status 与 FCL 属性合并；单列一张关联表承接，避免主时间线表过宽。</t>
+          <t>把事实表里散落的里程碑/状态按业务规则(GEN_FCL_DETAIL CASE)收敛成 1 行/贷款的可读时间线；退出原因直接取 servicer 的 fcremovaldesc(无解码表)。</t>
         </is>
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>查某贷款 stage 分组依据、关联诉讼/清算/违约属性。</t>
+          <t>查某贷款法拍‘何时进入各里程碑/当前状态/在法拍多少天/为何退出’。</t>
         </is>
       </c>
       <c r="H13" s="6" t="inlineStr">
         <is>
-          <t>1 行/贷款（最新 dataasof）。</t>
+          <t>1 行/贷款（含在途 + 已结）。</t>
         </is>
       </c>
       <c r="I13" s="6" t="inlineStr">
         <is>
-          <t>{ port.basic_data_loan_fcl(FCL 属性) + port.basic_data_daily_loan_common_clean.delinq(逾期码) } → port.basic_data_fcl_related〔basic_data_pool_config.py〕</t>
+          <t>… → port.basic_data_loan_fcl → port.basic_data_loan_foreclosure〔GEN_FCL_DETAIL basic_data_pool_config.py:253-305；状态 CASE :273；司法 :277-279；在法拍天数 :1628〕</t>
         </is>
       </c>
       <c r="J13" s="6" t="inlineStr">
         <is>
-          <t>port.basic_data_loan_fcl、port.basic_data_daily_loan_common_clean</t>
+          <t>port.basic_data_loan_fcl、tempfc.temp_basic_data_fcl、newrez.portnewrezfc、Servicer 文件(L0)</t>
         </is>
       </c>
       <c r="K13" s="6" t="inlineStr">
         <is>
-          <t>basic_data_fcl_related.delq_status → port.fcl_stage_info.group(stage 分组) → bpms.sync_fcl_stage_info → 视图 → BPS Stage 面板</t>
+          <t>basic_data_loan_foreclosure → (Redshift→MySQL 同步 df_db_util.py:665-699 sync_to_mysql / 702-726 update_to_mysql) → bpms.sync_loan_foreclosure〔GEN_FORECLOSURE asset_managment_config.py:535-608；实时天数校正 :597-598〕 → bpms.biz_data_view_loan_details_foreclosure(视图) → BPS Summary/Timeline 面板</t>
         </is>
       </c>
       <c r="L13" s="6" t="inlineStr">
         <is>
-          <t>port.fcl_stage_info、bpms.sync_fcl_stage_info、bpms.biz_data_view_loan_details_foreclosure</t>
+          <t>bpms.sync_loan_foreclosure、bpms.biz_data_view_loan_details_foreclosure</t>
         </is>
       </c>
       <c r="M13" s="6" t="inlineStr"/>
@@ -1810,125 +1814,129 @@
     <row r="14" ht="96" customHeight="1">
       <c r="A14" s="16" t="inlineStr">
         <is>
-          <t>⑬ port.fcl_stage_info</t>
+          <t>⑫ port.basic_data_fcl_related</t>
         </is>
       </c>
       <c r="B14" s="16" t="inlineStr">
         <is>
-          <t>L4 阶段表（Redshift）</t>
+          <t>L4 FCL 关联/过滤中间表</t>
         </is>
       </c>
       <c r="C14" s="16" t="inlineStr">
         <is>
-          <t>Redshift 阶段表(48 列)——把法拍拆成 6 大阶段，每阶段 5 维(开始/天数/扣除 LM-Hold 重叠等)，每贷款最新 fctrdt。</t>
+          <t>FCL 关联属性中间表(14 列)——诉讼标志、清算类型、BK 标志、违约原因、delq_status 等。</t>
         </is>
       </c>
       <c r="D14" s="16" t="inlineStr">
         <is>
-          <t>bpms.sync_fcl_stage_info(BPS 聚合 Stage/Timeline)的上游；面板‘各阶段停留天数’的底座。</t>
+          <t>给 stage 计算与过滤提供‘关联属性/分组键’(delq_status → stage group)。</t>
         </is>
       </c>
       <c r="E14" s="16" t="inlineStr">
         <is>
-          <t>阶段量化点（L4）：把法拍拆 6 阶段算停留天数（扣 LM/Hold 重叠），作 BPS Stage 面板上游。</t>
+          <t>分组键提供者（L4）：把 5 张 Newrez 原始表(general/liq/pmt/bk/prop)+ Carrington 源的关联属性合并，为 stage 计算提供分组键（delq_status→group）。</t>
         </is>
       </c>
       <c r="F14" s="16" t="inlineStr">
         <is>
-          <t>业务关心‘卡在哪一步多久’；阶段口径复杂(N:N 扣 LM/Hold 重叠)，单列一张表算清，并 JOIN portfunding 取 funding 维。</t>
+          <t>把 5 张 Newrez 原始表(general/liq/pmt/bk/prop)与 Carrington 源(portcarrington)的【诉讼/清算/BK/违约/逾期分类】按 loanid+dataasof 合并成一张窄关联表(1 行/贷款)，供 ⑬ stage 计算取 delq_status 作分组键(group)；单列一张承接，避免主时间线表过宽。注：delq_status 由 g.delinquency_status_mba + days360(pmt.nextduedate, dataasof) 现算，并非取自逾期支线 daily_loan_common_clean。</t>
         </is>
       </c>
       <c r="G14" s="16" t="inlineStr">
         <is>
-          <t>查某贷款‘在每个阶段停留多久、扣除 LM/Hold 后净时长、当前在哪个阶段组’。</t>
+          <t>查某贷款 stage 分组依据、关联诉讼/清算/违约属性。</t>
         </is>
       </c>
       <c r="H14" s="16" t="inlineStr">
         <is>
-          <t>1 行/贷款/fctrdt。</t>
+          <t>1 行/贷款（最新 dataasof）。</t>
         </is>
       </c>
       <c r="I14" s="16" t="inlineStr">
         <is>
-          <t>{ port.basic_data_loan_fcl + port.basic_data_fcl_related(delq_status 分组) + port.portfunding(JOIN) } → port.fcl_stage_info〔GEN_FCL_STAGE basic_data_pool_config.py:1774-2440〕</t>
+          <t>{ newrez.portnewrezgeneral(g) + newrez.portnewrezliq(l) + newrez.portnewrezpmt(pmt) + newrez.portnewrezbk(bk) + newrez.portnewrezprop(pr)，按 loanid+dataasof JOIN }〔Newrez 分支〕 UNION { carrington.portcarrington(c) }〔Carrington 分支〕 → port.basic_data_fcl_related〔CREATE_FCL_RELATE_ATTR basic_data_pool_config.py:1696-1770〕</t>
         </is>
       </c>
       <c r="J14" s="16" t="inlineStr">
         <is>
-          <t>port.basic_data_loan_fcl、port.basic_data_fcl_related、port.basic_data_daily_loan_common_clean、port.portfunding</t>
+          <t>newrez.portnewrezgeneral、newrez.portnewrezliq、newrez.portnewrezpmt、newrez.portnewrezbk、newrez.portnewrezprop、carrington.portcarrington</t>
         </is>
       </c>
       <c r="K14" s="16" t="inlineStr">
         <is>
-          <t>fcl_stage_info → bpms.sync_fcl_stage_info〔GET_FCL_STAGE_DATA asset_managment_config.py:925-929，JOIN port.portfunding〕 → 视图 → BPS Stage 面板</t>
+          <t>basic_data_fcl_related.delq_status → port.fcl_stage_info.group(stage 分组) → bpms.sync_fcl_stage_info → 视图 → BPS Stage 面板</t>
         </is>
       </c>
       <c r="L14" s="16" t="inlineStr">
         <is>
-          <t>bpms.sync_fcl_stage_info、bpms.biz_data_view_loan_details_foreclosure</t>
-        </is>
-      </c>
-      <c r="M14" s="16" t="inlineStr"/>
+          <t>port.fcl_stage_info、bpms.sync_fcl_stage_info、bpms.biz_data_view_loan_details_foreclosure</t>
+        </is>
+      </c>
+      <c r="M14" s="16" t="inlineStr">
+        <is>
+          <t>上游为 5 张 Newrez 原始表(general/liq/pmt/bk/prop) + carrington.portcarrington（代码 CREATE_FCL_RELATE_ATTR pool:1696-1770 实测，按 loanid+dataasof JOIN 后 UNION）；并非 basic_data_loan_fcl / daily_loan_common_clean（旧元数据误标，2026-06-15 经 Code-First 订正）。SQL 表别名：g=portnewrezgeneral、l=portnewrezliq、pmt=portnewrezpmt、bk=portnewrezbk、pr=portnewrezprop、c=portcarrington。</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="96" customHeight="1">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>⑭ port.portfunding</t>
+          <t>⑬ port.fcl_stage_info</t>
         </is>
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>L4 维度（融资池）</t>
+          <t>L4 阶段表（Redshift）</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>融资池表(57 列，1 行/贷款)——funding/deal 标识(fundingid/dealid)与池属性。</t>
+          <t>Redshift 阶段表(48 列)——把法拍拆成 6 大阶段，每阶段 5 维(开始/天数/扣除 LM-Hold 重叠等)，每贷款最新 fctrdt。</t>
         </is>
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>作为 JOIN 维度为 FCL 输出补 funding_id/bid_id，并做入库过滤。</t>
+          <t>bpms.sync_fcl_stage_info(BPS 聚合 Stage/Timeline)的上游；面板‘各阶段停留天数’的底座。</t>
         </is>
       </c>
       <c r="E15" s="6" t="inlineStr">
         <is>
-          <t>JOIN 维度（L4）：运行时为 FCL 输出补 funding_id/bid_id，并做入库过滤（按融资池/deal）。</t>
+          <t>阶段量化点（L4）：把法拍拆 6 阶段算停留天数（扣 LM/Hold 重叠），作 BPS Stage 面板上游。</t>
         </is>
       </c>
       <c r="F15" s="6" t="inlineStr">
         <is>
-          <t>BPS 需按 funding/bid 维展示与归集；FCL 表本身不含，运行时 JOIN portfunding 补齐(dealid→bid_id, fundingid→funding_id)。</t>
+          <t>业务关心‘卡在哪一步多久’；阶段口径复杂(N:N 扣 LM/Hold 重叠)，单列一张表算清，并 JOIN portfunding 取 funding 维。</t>
         </is>
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>查某贷款属于哪个融资池/deal，或为何被 sync 过滤进/出。</t>
+          <t>查某贷款‘在每个阶段停留多久、扣除 LM/Hold 后净时长、当前在哪个阶段组’。</t>
         </is>
       </c>
       <c r="H15" s="6" t="inlineStr">
         <is>
-          <t>1 行/贷款（当前态）。</t>
+          <t>1 行/贷款/fctrdt。</t>
         </is>
       </c>
       <c r="I15" s="6" t="inlineStr">
         <is>
-          <t>投资/融资域(非 servicer FCL 文件) → port.portfunding</t>
+          <t>{ port.basic_data_loan_fcl + port.basic_data_fcl_related(delq_status 分组) + port.basic_data_loan_foreclosure_loss_mitigation + port.basic_data_loan_foreclosure_hold(算 in_lm/on_hold) + port.portfunding(JOIN) } → port.fcl_stage_info〔GEN_FCL_STAGE basic_data_pool_config.py:1774-2440〕</t>
         </is>
       </c>
       <c r="J15" s="6" t="inlineStr">
         <is>
-          <t>投资/融资域来源（非 FCL servicer 文件）</t>
+          <t>port.basic_data_loan_fcl、port.basic_data_fcl_related、port.basic_data_loan_foreclosure_loss_mitigation、port.basic_data_loan_foreclosure_hold、port.portfunding</t>
         </is>
       </c>
       <c r="K15" s="6" t="inlineStr">
         <is>
-          <t>portfunding ⋈ { port.fcl_stage_info / GEN_FORECLOSURE(asset_managment_config.py:535-608) } → bpms.sync_fcl_stage_info / bpms.sync_loan_foreclosure → 视图 → BPS</t>
+          <t>fcl_stage_info → bpms.sync_fcl_stage_info〔GET_FCL_STAGE_DATA asset_managment_config.py:925-929，JOIN port.portfunding〕 → 视图 → BPS Stage 面板</t>
         </is>
       </c>
       <c r="L15" s="6" t="inlineStr">
         <is>
-          <t>port.fcl_stage_info、bpms.sync_fcl_stage_info、bpms.sync_loan_foreclosure、bpms.biz_data_view_loan_details_foreclosure</t>
+          <t>bpms.sync_fcl_stage_info、bpms.biz_data_view_loan_details_foreclosure</t>
         </is>
       </c>
       <c r="M15" s="6" t="inlineStr"/>
@@ -1936,62 +1944,62 @@
     <row r="16" ht="96" customHeight="1">
       <c r="A16" s="16" t="inlineStr">
         <is>
-          <t>⑮ port.basic_data_loan_foreclosure_hold</t>
+          <t>⑭ port.portfunding</t>
         </is>
       </c>
       <c r="B16" s="16" t="inlineStr">
         <is>
-          <t>L4 Hold 历史（Redshift 长表）</t>
+          <t>L4 维度（融资池）</t>
         </is>
       </c>
       <c r="C16" s="16" t="inlineStr">
         <is>
-          <t>Redshift Hold 历史(长表，1 行/Hold)——把源表 4 个 Hold 槽(fchold1..4)拆成长格式；Carrington 多 Hold 先排名压进 4 槽。</t>
+          <t>融资池表(57 列，1 行/贷款)——funding/deal 标识(fundingid/dealid)与池属性。</t>
         </is>
       </c>
       <c r="D16" s="16" t="inlineStr">
         <is>
-          <t>bpms.sync_loan_foreclosure_hold(BPS Hold 全历史)的上游；支撑‘一笔法拍多个 Hold’。</t>
+          <t>作为 JOIN 维度为 FCL 输出补 funding_id/bid_id，并做入库过滤。</t>
         </is>
       </c>
       <c r="E16" s="16" t="inlineStr">
         <is>
-          <t>拆槽长表（L4）：把源表 4 个 Hold 宽槽 unpivot 成 1 行/Hold 的全历史，作 BPS Hold 面板上游。</t>
+          <t>JOIN 维度（L4）：运行时为 FCL 输出补 funding_id/bid_id，并做入库过滤（按融资池/deal）。</t>
         </is>
       </c>
       <c r="F16" s="16" t="inlineStr">
         <is>
-          <t>源表把 Hold 压成 4 个宽槽，业务要全历史，需拆槽(unpivot)成 1 行/Hold；一笔 FCL 多 Hold 是常态(非数据错误)。</t>
+          <t>BPS 需按 funding/bid 维展示与归集；FCL 表本身不含，运行时 JOIN portfunding 补齐(dealid→bid_id, fundingid→funding_id)。</t>
         </is>
       </c>
       <c r="G16" s="16" t="inlineStr">
         <is>
-          <t>查某贷款全部 Hold 的起止/原因/历史。</t>
+          <t>查某贷款属于哪个融资池/deal，或为何被 sync 过滤进/出。</t>
         </is>
       </c>
       <c r="H16" s="16" t="inlineStr">
         <is>
-          <t>1 行/贷款/Hold 段。</t>
+          <t>1 行/贷款（当前态）。</t>
         </is>
       </c>
       <c r="I16" s="16" t="inlineStr">
         <is>
-          <t>newrez.portnewrezfc(fchold1..4) → port.basic_data_loan_fcl → port.basic_data_loan_foreclosure_hold〔拆槽 basic_data_pool_config.py:466-768；Carrington 排名 :504-629〕</t>
+          <t>投资/融资域(非 servicer FCL 文件) → port.portfunding</t>
         </is>
       </c>
       <c r="J16" s="16" t="inlineStr">
         <is>
-          <t>newrez.portnewrezfc、port.basic_data_loan_fcl</t>
+          <t>投资/融资域来源（非 FCL servicer 文件）</t>
         </is>
       </c>
       <c r="K16" s="16" t="inlineStr">
         <is>
-          <t>→ bpms.sync_loan_foreclosure_hold〔GEN_FORECLOSURE_HOLD asset_managment_config.py:847-894〕 → 视图 → BPS Hold 面板</t>
+          <t>portfunding ⋈ { port.fcl_stage_info / GEN_FORECLOSURE(asset_managment_config.py:535-608) } → bpms.sync_fcl_stage_info / bpms.sync_loan_foreclosure → 视图 → BPS</t>
         </is>
       </c>
       <c r="L16" s="16" t="inlineStr">
         <is>
-          <t>bpms.sync_loan_foreclosure_hold、bpms.biz_data_view_loan_details_foreclosure</t>
+          <t>port.fcl_stage_info、bpms.sync_fcl_stage_info、bpms.sync_loan_foreclosure、bpms.biz_data_view_loan_details_foreclosure</t>
         </is>
       </c>
       <c r="M16" s="16" t="inlineStr"/>
@@ -1999,62 +2007,62 @@
     <row r="17" ht="96" customHeight="1">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>⑯ port.basic_data_loan_foreclosure_loss_mitigation</t>
+          <t>⑮ port.basic_data_loan_foreclosure_hold</t>
         </is>
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>L4 LM 历史（Redshift）</t>
+          <t>L4 Hold 历史（Redshift 长表）</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>Redshift LM 历史(1 行/LM 周期)——按 (loanid, dealstartdate)，datadic 解码 lmdeal/lmprogram/lmstatus/lmdecision。</t>
+          <t>Redshift Hold 历史(长表，1 行/Hold)——把源表 4 个 Hold 槽(fchold1..4)拆成长格式；Carrington 多 Hold 先排名压进 4 槽。</t>
         </is>
       </c>
       <c r="D17" s="6" t="inlineStr">
         <is>
-          <t>bpms.sync_loan_foreclosure_loss_mitigation 的上游；支撑‘一笔贷款多 LM 周期’。</t>
+          <t>bpms.sync_loan_foreclosure_hold(BPS Hold 全历史)的上游；支撑‘一笔法拍多个 Hold’。</t>
         </is>
       </c>
       <c r="E17" s="6" t="inlineStr">
         <is>
-          <t>解码历史表（L4）：按 LM 周期经 datadic 解码 lmdeal/lmprogram/lmstatus/lmdecision，作 BPS LM 面板上游。</t>
+          <t>拆槽长表（L4）：把源表 4 个 Hold 宽槽 unpivot 成 1 行/Hold 的全历史，作 BPS Hold 面板上游。</t>
         </is>
       </c>
       <c r="F17" s="6" t="inlineStr">
         <is>
-          <t>LM 多周期是常态；编码需经 datadic 解码成业务文案(JOIN key 拼 code+'.0')。</t>
+          <t>源表把 Hold 压成 4 个宽槽，业务要全历史，需拆槽(unpivot)成 1 行/Hold；一笔 FCL 多 Hold 是常态(非数据错误)。</t>
         </is>
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>查某贷款全部 LM 周期/项目/决定(已解码)。</t>
+          <t>查某贷款全部 Hold 的起止/原因/历史。</t>
         </is>
       </c>
       <c r="H17" s="6" t="inlineStr">
         <is>
-          <t>1 行/贷款/LM 周期。</t>
+          <t>1 行/贷款/Hold 段。</t>
         </is>
       </c>
       <c r="I17" s="6" t="inlineStr">
         <is>
-          <t>{ newrez.portnewrezlm + newrez.portnewrezdatadic } → port.basic_data_loan_fcl 体系 → port.basic_data_loan_foreclosure_loss_mitigation〔basic_data_pool_config.py:799-843〕</t>
+          <t>newrez.portnewrezfc(fchold1..4) → port.basic_data_loan_fcl → port.basic_data_loan_foreclosure_hold〔拆槽 basic_data_pool_config.py:466-768；Carrington 排名 :504-629〕</t>
         </is>
       </c>
       <c r="J17" s="6" t="inlineStr">
         <is>
-          <t>newrez.portnewrezlm、newrez.portnewrezdatadic、port.basic_data_loan_fcl</t>
+          <t>newrez.portnewrezfc、port.basic_data_loan_fcl</t>
         </is>
       </c>
       <c r="K17" s="6" t="inlineStr">
         <is>
-          <t>→ bpms.sync_loan_foreclosure_loss_mitigation〔asset_managment_config.py:799-819〕 → 视图 → BPS LM 面板</t>
+          <t>→ bpms.sync_loan_foreclosure_hold〔GEN_FORECLOSURE_HOLD asset_managment_config.py:847-894〕 → 视图 → BPS Hold 面板</t>
         </is>
       </c>
       <c r="L17" s="6" t="inlineStr">
         <is>
-          <t>bpms.sync_loan_foreclosure_loss_mitigation、bpms.biz_data_view_loan_details_foreclosure</t>
+          <t>bpms.sync_loan_foreclosure_hold、bpms.biz_data_view_loan_details_foreclosure</t>
         </is>
       </c>
       <c r="M17" s="6" t="inlineStr"/>
@@ -2062,62 +2070,62 @@
     <row r="18" ht="96" customHeight="1">
       <c r="A18" s="16" t="inlineStr">
         <is>
-          <t>⑰ port.basic_data_loan_foreclosure_bankruptcy</t>
+          <t>⑯ port.basic_data_loan_foreclosure_loss_mitigation</t>
         </is>
       </c>
       <c r="B18" s="16" t="inlineStr">
         <is>
-          <t>L4 破产历史（Redshift）</t>
+          <t>L4 LM 历史（Redshift）</t>
         </is>
       </c>
       <c r="C18" s="16" t="inlineStr">
         <is>
-          <t>Redshift 破产历史(1 行/破产申请)——datadic 解码 bkstatus；Carrington 专有 mfr_filed_date(Newrez 为 NULL)。</t>
+          <t>Redshift LM 历史(1 行/LM 周期)——按 (loanid, dealstartdate)，datadic 解码 lmdeal/lmprogram/lmstatus/lmdecision。</t>
         </is>
       </c>
       <c r="D18" s="16" t="inlineStr">
         <is>
-          <t>bpms.sync_loan_foreclosure_bankruptcy 的上游。</t>
+          <t>bpms.sync_loan_foreclosure_loss_mitigation 的上游；支撑‘一笔贷款多 LM 周期’。</t>
         </is>
       </c>
       <c r="E18" s="16" t="inlineStr">
         <is>
-          <t>解码历史表（L4）：按破产申请经 datadic 解码 bkstatus，作 BPS 破产面板上游。</t>
+          <t>解码历史表（L4）：按 LM 周期经 datadic 解码 lmdeal/lmprogram/lmstatus/lmdecision，作 BPS LM 面板上游。</t>
         </is>
       </c>
       <c r="F18" s="16" t="inlineStr">
         <is>
-          <t>破产可多次申请；编码经 datadic 解码。</t>
+          <t>LM 多周期是常态；编码需经 datadic 解码成业务文案(JOIN key 拼 code+'.0')。</t>
         </is>
       </c>
       <c r="G18" s="16" t="inlineStr">
         <is>
-          <t>查某贷款全部破产申请/章节/状态(已解码)。</t>
+          <t>查某贷款全部 LM 周期/项目/决定(已解码)。</t>
         </is>
       </c>
       <c r="H18" s="16" t="inlineStr">
         <is>
-          <t>1 行/贷款/破产申请。</t>
+          <t>1 行/贷款/LM 周期。</t>
         </is>
       </c>
       <c r="I18" s="16" t="inlineStr">
         <is>
-          <t>{ newrez.portnewrezbk + newrez.portnewrezdatadic } → port.basic_data_loan_foreclosure_bankruptcy〔basic_data_pool_config.py:331-370〕</t>
+          <t>{ newrez.portnewrezlm + newrez.portnewrezdatadic } → port.basic_data_loan_fcl 体系 → port.basic_data_loan_foreclosure_loss_mitigation〔basic_data_pool_config.py:799-843〕</t>
         </is>
       </c>
       <c r="J18" s="16" t="inlineStr">
         <is>
-          <t>newrez.portnewrezbk、newrez.portnewrezdatadic、port.basic_data_loan_fcl</t>
+          <t>newrez.portnewrezlm、newrez.portnewrezdatadic、port.basic_data_loan_fcl</t>
         </is>
       </c>
       <c r="K18" s="16" t="inlineStr">
         <is>
-          <t>→ bpms.sync_loan_foreclosure_bankruptcy〔asset_managment_config.py:822-843〕 → 视图 → BPS 破产面板</t>
+          <t>→ bpms.sync_loan_foreclosure_loss_mitigation〔asset_managment_config.py:799-819〕 → 视图 → BPS LM 面板</t>
         </is>
       </c>
       <c r="L18" s="16" t="inlineStr">
         <is>
-          <t>bpms.sync_loan_foreclosure_bankruptcy、bpms.biz_data_view_loan_details_foreclosure</t>
+          <t>bpms.sync_loan_foreclosure_loss_mitigation、bpms.biz_data_view_loan_details_foreclosure</t>
         </is>
       </c>
       <c r="M18" s="16" t="inlineStr"/>
@@ -2125,124 +2133,120 @@
     <row r="19" ht="96" customHeight="1">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>⑱ bpms.sync_loan_foreclosure</t>
+          <t>⑰ port.basic_data_loan_foreclosure_bankruptcy</t>
         </is>
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>L5 BPS 直接对接（主表）</t>
+          <t>L4 破产历史（Redshift）</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>BPS 法拍主表(72 列，当前态)——Summary/Timeline/target 主面板的数据源。</t>
+          <t>Redshift 破产历史(1 行/破产申请)——datadic 解码 bkstatus；Carrington 专有 mfr_filed_date(Newrez 为 NULL)。</t>
         </is>
       </c>
       <c r="D19" s="6" t="inlineStr">
         <is>
-          <t>BPS 直接对接表；法拍主面板。</t>
+          <t>bpms.sync_loan_foreclosure_bankruptcy 的上游。</t>
         </is>
       </c>
       <c r="E19" s="6" t="inlineStr">
         <is>
-          <t>L4→MySQL 落库对接（L5）：法拍主面板数据源；覆盖更新并对天数做当日实时校正。</t>
+          <t>解码历史表（L4）：按破产申请经 datadic 解码 bkstatus，作 BPS 破产面板上游。</t>
         </is>
       </c>
       <c r="F19" s="6" t="inlineStr">
         <is>
-          <t>L4 算好后同步到 MySQL 供 BPS 读；采用覆盖更新(coverage upsert)，并对天数做 NY 当日实时校正(+DATEDIFF)。</t>
+          <t>破产可多次申请；编码经 datadic 解码。</t>
         </is>
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>查 BPS 主面板某字段的落库值、排查面板与 Redshift 是否一致。</t>
+          <t>查某贷款全部破产申请/章节/状态(已解码)。</t>
         </is>
       </c>
       <c r="H19" s="6" t="inlineStr">
         <is>
-          <t>1 行/贷款（过滤 timeline_referred… IS NOT NULL，即已进入法拍）。</t>
+          <t>1 行/贷款/破产申请。</t>
         </is>
       </c>
       <c r="I19" s="6" t="inlineStr">
         <is>
-          <t>… → port.basic_data_loan_foreclosure(Redshift) → (sync_to_mysql/update_to_mysql df_db_util.py:665-726) → bpms.sync_loan_foreclosure〔GEN_FORECLOSURE asset_managment_config.py:535-608〕（JOIN port.portfunding 取 funding_id/bid_id）</t>
+          <t>{ newrez.portnewrezbk + newrez.portnewrezdatadic } → port.basic_data_loan_foreclosure_bankruptcy〔basic_data_pool_config.py:331-370〕</t>
         </is>
       </c>
       <c r="J19" s="6" t="inlineStr">
         <is>
-          <t>port.basic_data_loan_foreclosure、port.portfunding、port.basic_data_loan_fcl</t>
+          <t>newrez.portnewrezbk、newrez.portnewrezdatadic、port.basic_data_loan_fcl</t>
         </is>
       </c>
       <c r="K19" s="6" t="inlineStr">
         <is>
-          <t>→ bpms.biz_data_view_loan_details_foreclosure(视图) → BPS 法拍详情/主面板</t>
+          <t>→ bpms.sync_loan_foreclosure_bankruptcy〔asset_managment_config.py:822-843〕 → 视图 → BPS 破产面板</t>
         </is>
       </c>
       <c r="L19" s="6" t="inlineStr">
         <is>
-          <t>bpms.biz_data_view_loan_details_foreclosure</t>
-        </is>
-      </c>
-      <c r="M19" s="6" t="inlineStr">
-        <is>
-          <t>样例 Loan5(纯 Chapter 13 BK，未进法拍)不在本表，故本 dump 命中 4/5。</t>
-        </is>
-      </c>
+          <t>bpms.sync_loan_foreclosure_bankruptcy、bpms.biz_data_view_loan_details_foreclosure</t>
+        </is>
+      </c>
+      <c r="M19" s="6" t="inlineStr"/>
     </row>
     <row r="20" ht="96" customHeight="1">
       <c r="A20" s="16" t="inlineStr">
         <is>
-          <t>⑲ bpms.sync_fcl_stage_info</t>
+          <t>⑱ bpms.sync_loan_foreclosure</t>
         </is>
       </c>
       <c r="B20" s="16" t="inlineStr">
         <is>
-          <t>L5 BPS 直接对接（阶段聚合）</t>
+          <t>L5 BPS 直接对接（主表）</t>
         </is>
       </c>
       <c r="C20" s="16" t="inlineStr">
         <is>
-          <t>BPS 聚合 Stage/Timeline 表(57 列)——各阶段停留天数/时间线。</t>
+          <t>BPS 法拍主表(72 列，当前态)——Summary/Timeline/target 主面板的数据源。</t>
         </is>
       </c>
       <c r="D20" s="16" t="inlineStr">
         <is>
-          <t>BPS Stage 面板数据源。</t>
+          <t>BPS 直接对接表；法拍主面板。</t>
         </is>
       </c>
       <c r="E20" s="16" t="inlineStr">
         <is>
-          <t>L4→MySQL 落库对接（L5）：BPS Stage/Timeline 面板数据源（JOIN portfunding 带 funding 维）。</t>
+          <t>L4→MySQL 落库对接（L5）：法拍主面板数据源；覆盖更新并对天数做当日实时校正。</t>
         </is>
       </c>
       <c r="F20" s="16" t="inlineStr">
         <is>
-          <t>阶段口径在 Redshift 算清后同步；JOIN portfunding 带 funding 维。</t>
+          <t>L4 算好后同步到 MySQL 供 BPS 读；采用覆盖更新(coverage upsert)，并对天数做 NY 当日实时校正(+DATEDIFF)。</t>
         </is>
       </c>
       <c r="G20" s="16" t="inlineStr">
         <is>
-          <t>查 BPS 各阶段天数落库值。</t>
+          <t>查 BPS 主面板某字段的落库值、排查面板与 Redshift 是否一致。</t>
         </is>
       </c>
       <c r="H20" s="16" t="inlineStr">
         <is>
-          <t>1 行/贷款/fctrdt（过滤 activefcflag=1 且 fcremovaldate IS NULL）。</t>
+          <t>1 行/贷款（过滤 timeline_referred… IS NOT NULL，即已进入法拍）。</t>
         </is>
       </c>
       <c r="I20" s="16" t="inlineStr">
         <is>
-          <t>port.fcl_stage_info(⋈ port.portfunding) → bpms.sync_fcl_stage_info〔GET_FCL_STAGE_DATA asset_managment_config.py:925-929〕</t>
+          <t>… → port.basic_data_loan_foreclosure(Redshift) → (sync_to_mysql/update_to_mysql df_db_util.py:665-726) → bpms.sync_loan_foreclosure〔GEN_FORECLOSURE asset_managment_config.py:535-608〕（JOIN port.portfunding 取 funding_id/bid_id）</t>
         </is>
       </c>
       <c r="J20" s="16" t="inlineStr">
         <is>
-          <t>port.fcl_stage_info、port.portfunding</t>
+          <t>port.basic_data_loan_foreclosure、port.portfunding、port.basic_data_loan_fcl</t>
         </is>
       </c>
       <c r="K20" s="16" t="inlineStr">
         <is>
-          <t>→ bpms.biz_data_view_loan_details_foreclosure(视图) → BPS Stage 面板</t>
+          <t>→ bpms.biz_data_view_loan_details_foreclosure(视图) → BPS 法拍详情/主面板</t>
         </is>
       </c>
       <c r="L20" s="16" t="inlineStr">
@@ -2250,67 +2254,71 @@
           <t>bpms.biz_data_view_loan_details_foreclosure</t>
         </is>
       </c>
-      <c r="M20" s="16" t="inlineStr"/>
+      <c r="M20" s="16" t="inlineStr">
+        <is>
+          <t>样例 Loan5(纯 Chapter 13 BK，未进法拍)不在本表，故本 dump 命中 4/5。</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="96" customHeight="1">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>⑳ bpms.biz_data_view_loan_details_foreclosure</t>
+          <t>⑲ bpms.sync_fcl_stage_info</t>
         </is>
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>L5 BPS 详情页视图</t>
+          <t>L5 BPS 直接对接（阶段聚合）</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>BPS 法拍详情页视图(104 列)——把主表 + stage + hold + lm + bk 用 LEFT JOIN 拼成详情页；含 actual/var 天数。</t>
+          <t>BPS 聚合 Stage/Timeline 表(57 列)——各阶段停留天数/时间线。</t>
         </is>
       </c>
       <c r="D21" s="6" t="inlineStr">
         <is>
-          <t>BPS 详情页的‘一站式’读取视图。</t>
+          <t>BPS Stage 面板数据源。</t>
         </is>
       </c>
       <c r="E21" s="6" t="inlineStr">
         <is>
-          <t>一站式聚合视图（L5）：LEFT JOIN 主表+stage+hold+lm+bk 共 5 张 sync 表，供详情页一次性读取。</t>
+          <t>L4→MySQL 落库对接（L5）：BPS Stage/Timeline 面板数据源（JOIN portfunding 带 funding 维）。</t>
         </is>
       </c>
       <c r="F21" s="6" t="inlineStr">
         <is>
-          <t>详情页要跨 5 张面板表聚合，用视图免去前端多次查询。</t>
+          <t>阶段口径在 Redshift 算清后同步；JOIN portfunding 带 funding 维。</t>
         </is>
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>查详情页某列从哪几张 sync 表拼来、actual vs target 差异。</t>
+          <t>查 BPS 各阶段天数落库值。</t>
         </is>
       </c>
       <c r="H21" s="6" t="inlineStr">
         <is>
-          <t>1 行/贷款/fctrdt（取最新）。</t>
+          <t>1 行/贷款/fctrdt（过滤 activefcflag=1 且 fcremovaldate IS NULL）。</t>
         </is>
       </c>
       <c r="I21" s="6" t="inlineStr">
         <is>
-          <t>{ bpms.sync_loan_foreclosure + bpms.sync_fcl_stage_info + bpms.sync_loan_foreclosure_hold + bpms.sync_loan_foreclosure_loss_mitigation + bpms.sync_loan_foreclosure_bankruptcy } → 视图(LEFT JOIN，104 列)</t>
+          <t>port.fcl_stage_info(⋈ port.portfunding) → bpms.sync_fcl_stage_info〔GET_FCL_STAGE_DATA asset_managment_config.py:925-929〕</t>
         </is>
       </c>
       <c r="J21" s="6" t="inlineStr">
         <is>
-          <t>bpms.sync_loan_foreclosure、bpms.sync_fcl_stage_info、bpms.sync_loan_foreclosure_hold、bpms.sync_loan_foreclosure_loss_mitigation、bpms.sync_loan_foreclosure_bankruptcy</t>
+          <t>port.fcl_stage_info、port.portfunding</t>
         </is>
       </c>
       <c r="K21" s="6" t="inlineStr">
         <is>
-          <t>→ BPS 法拍详情页 UI（5 面板）</t>
+          <t>→ bpms.biz_data_view_loan_details_foreclosure(视图) → BPS Stage 面板</t>
         </is>
       </c>
       <c r="L21" s="6" t="inlineStr">
         <is>
-          <t>BPS 法拍详情页 UI</t>
+          <t>bpms.biz_data_view_loan_details_foreclosure</t>
         </is>
       </c>
       <c r="M21" s="6" t="inlineStr"/>
@@ -2318,62 +2326,62 @@
     <row r="22" ht="96" customHeight="1">
       <c r="A22" s="16" t="inlineStr">
         <is>
-          <t>㉑ bpms.sync_loan_foreclosure_hold</t>
+          <t>⑳ bpms.biz_data_view_loan_details_foreclosure</t>
         </is>
       </c>
       <c r="B22" s="16" t="inlineStr">
         <is>
-          <t>L5 BPS 直接对接（Hold 历史）</t>
+          <t>L5 BPS 详情页视图</t>
         </is>
       </c>
       <c r="C22" s="16" t="inlineStr">
         <is>
-          <t>BPS Hold 全历史(每次变更一行)。</t>
+          <t>BPS 法拍详情页视图(104 列)——把主表 + stage + hold + lm + bk 用 LEFT JOIN 拼成详情页；含 actual/var 天数。</t>
         </is>
       </c>
       <c r="D22" s="16" t="inlineStr">
         <is>
-          <t>BPS Hold 面板。</t>
+          <t>BPS 详情页的‘一站式’读取视图。</t>
         </is>
       </c>
       <c r="E22" s="16" t="inlineStr">
         <is>
-          <t>L4→MySQL 落库对接（L5）：BPS Hold 面板数据源（每次 Hold 变更一行）。</t>
+          <t>一站式聚合视图（L5）：LEFT JOIN 主表+stage+hold+lm+bk 共 5 张 sync 表，供详情页一次性读取。</t>
         </is>
       </c>
       <c r="F22" s="16" t="inlineStr">
         <is>
-          <t>见 ⑫；L4 拆槽后同步覆盖更新。</t>
+          <t>详情页要跨 5 张面板表聚合，用视图免去前端多次查询。</t>
         </is>
       </c>
       <c r="G22" s="16" t="inlineStr">
         <is>
-          <t>查 BPS 上某贷款全部 Hold 落库记录。</t>
+          <t>查详情页某列从哪几张 sync 表拼来、actual vs target 差异。</t>
         </is>
       </c>
       <c r="H22" s="16" t="inlineStr">
         <is>
-          <t>1 行/Hold 段。</t>
+          <t>1 行/贷款/fctrdt（取最新）。</t>
         </is>
       </c>
       <c r="I22" s="16" t="inlineStr">
         <is>
-          <t>port.basic_data_loan_foreclosure_hold → bpms.sync_loan_foreclosure_hold〔asset_managment_config.py:847-894〕</t>
+          <t>{ bpms.sync_loan_foreclosure + bpms.sync_fcl_stage_info + bpms.sync_loan_foreclosure_hold + bpms.sync_loan_foreclosure_loss_mitigation + bpms.sync_loan_foreclosure_bankruptcy } → 视图(LEFT JOIN，104 列)</t>
         </is>
       </c>
       <c r="J22" s="16" t="inlineStr">
         <is>
-          <t>port.basic_data_loan_foreclosure_hold</t>
+          <t>bpms.sync_loan_foreclosure、bpms.sync_fcl_stage_info、bpms.sync_loan_foreclosure_hold、bpms.sync_loan_foreclosure_loss_mitigation、bpms.sync_loan_foreclosure_bankruptcy</t>
         </is>
       </c>
       <c r="K22" s="16" t="inlineStr">
         <is>
-          <t>→ bpms.biz_data_view_loan_details_foreclosure(视图) → BPS Hold 面板</t>
+          <t>→ BPS 法拍详情页 UI（5 面板）</t>
         </is>
       </c>
       <c r="L22" s="16" t="inlineStr">
         <is>
-          <t>bpms.biz_data_view_loan_details_foreclosure</t>
+          <t>BPS 法拍详情页 UI</t>
         </is>
       </c>
       <c r="M22" s="16" t="inlineStr"/>
@@ -2381,57 +2389,57 @@
     <row r="23" ht="96" customHeight="1">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>㉒ bpms.sync_loan_foreclosure_loss_mitigation</t>
+          <t>㉑ bpms.sync_loan_foreclosure_hold</t>
         </is>
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>L5 BPS 直接对接（LM 周期历史）</t>
+          <t>L5 BPS 直接对接（Hold 历史）</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>BPS LM 周期历史(1 行/LM 周期，已解码)。</t>
+          <t>BPS Hold 全历史(每次变更一行)。</t>
         </is>
       </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
-          <t>BPS LM 面板。</t>
+          <t>BPS Hold 面板。</t>
         </is>
       </c>
       <c r="E23" s="6" t="inlineStr">
         <is>
-          <t>L4→MySQL 落库对接（L5）：BPS LM 面板数据源（1 行/LM 周期，已解码）。</t>
+          <t>L4→MySQL 落库对接（L5）：BPS Hold 面板数据源（每次 Hold 变更一行）。</t>
         </is>
       </c>
       <c r="F23" s="6" t="inlineStr">
         <is>
-          <t>见 ⑬；L4 解码后同步覆盖更新。</t>
+          <t>见 ⑫；L4 拆槽后同步覆盖更新。</t>
         </is>
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>查 BPS 上某贷款全部 LM 周期落库记录。</t>
+          <t>查 BPS 上某贷款全部 Hold 落库记录。</t>
         </is>
       </c>
       <c r="H23" s="6" t="inlineStr">
         <is>
-          <t>1 行/LM 周期。</t>
+          <t>1 行/Hold 段。</t>
         </is>
       </c>
       <c r="I23" s="6" t="inlineStr">
         <is>
-          <t>port.basic_data_loan_foreclosure_loss_mitigation → bpms.sync_loan_foreclosure_loss_mitigation〔asset_managment_config.py:799-819〕</t>
+          <t>port.basic_data_loan_foreclosure_hold → bpms.sync_loan_foreclosure_hold〔asset_managment_config.py:847-894〕</t>
         </is>
       </c>
       <c r="J23" s="6" t="inlineStr">
         <is>
-          <t>port.basic_data_loan_foreclosure_loss_mitigation</t>
+          <t>port.basic_data_loan_foreclosure_hold</t>
         </is>
       </c>
       <c r="K23" s="6" t="inlineStr">
         <is>
-          <t>→ bpms.biz_data_view_loan_details_foreclosure(视图) → BPS LM 面板</t>
+          <t>→ bpms.biz_data_view_loan_details_foreclosure(视图) → BPS Hold 面板</t>
         </is>
       </c>
       <c r="L23" s="6" t="inlineStr">
@@ -2444,57 +2452,57 @@
     <row r="24" ht="96" customHeight="1">
       <c r="A24" s="16" t="inlineStr">
         <is>
-          <t>㉓ bpms.sync_loan_foreclosure_bankruptcy</t>
+          <t>㉒ bpms.sync_loan_foreclosure_loss_mitigation</t>
         </is>
       </c>
       <c r="B24" s="16" t="inlineStr">
         <is>
-          <t>L5 BPS 直接对接（破产记录）</t>
+          <t>L5 BPS 直接对接（LM 周期历史）</t>
         </is>
       </c>
       <c r="C24" s="16" t="inlineStr">
         <is>
-          <t>BPS 破产记录(1 行/破产申请，已解码)。</t>
+          <t>BPS LM 周期历史(1 行/LM 周期，已解码)。</t>
         </is>
       </c>
       <c r="D24" s="16" t="inlineStr">
         <is>
-          <t>BPS 破产面板。</t>
+          <t>BPS LM 面板。</t>
         </is>
       </c>
       <c r="E24" s="16" t="inlineStr">
         <is>
-          <t>L4→MySQL 落库对接（L5）：BPS 破产面板数据源（1 行/破产申请，已解码）。</t>
+          <t>L4→MySQL 落库对接（L5）：BPS LM 面板数据源（1 行/LM 周期，已解码）。</t>
         </is>
       </c>
       <c r="F24" s="16" t="inlineStr">
         <is>
-          <t>见 ⑭；L4 解码后同步覆盖更新。</t>
+          <t>见 ⑬；L4 解码后同步覆盖更新。</t>
         </is>
       </c>
       <c r="G24" s="16" t="inlineStr">
         <is>
-          <t>查 BPS 上某贷款全部破产记录落库值。</t>
+          <t>查 BPS 上某贷款全部 LM 周期落库记录。</t>
         </is>
       </c>
       <c r="H24" s="16" t="inlineStr">
         <is>
-          <t>1 行/破产申请。</t>
+          <t>1 行/LM 周期。</t>
         </is>
       </c>
       <c r="I24" s="16" t="inlineStr">
         <is>
-          <t>port.basic_data_loan_foreclosure_bankruptcy → bpms.sync_loan_foreclosure_bankruptcy〔asset_managment_config.py:822-843〕</t>
+          <t>port.basic_data_loan_foreclosure_loss_mitigation → bpms.sync_loan_foreclosure_loss_mitigation〔asset_managment_config.py:799-819〕</t>
         </is>
       </c>
       <c r="J24" s="16" t="inlineStr">
         <is>
-          <t>port.basic_data_loan_foreclosure_bankruptcy</t>
+          <t>port.basic_data_loan_foreclosure_loss_mitigation</t>
         </is>
       </c>
       <c r="K24" s="16" t="inlineStr">
         <is>
-          <t>→ bpms.biz_data_view_loan_details_foreclosure(视图) → BPS 破产面板</t>
+          <t>→ bpms.biz_data_view_loan_details_foreclosure(视图) → BPS LM 面板</t>
         </is>
       </c>
       <c r="L24" s="16" t="inlineStr">
@@ -2507,68 +2515,131 @@
     <row r="25" ht="96" customHeight="1">
       <c r="A25" s="6" t="inlineStr">
         <is>
+          <t>㉓ bpms.sync_loan_foreclosure_bankruptcy</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="inlineStr">
+        <is>
+          <t>L5 BPS 直接对接（破产记录）</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t>BPS 破产记录(1 行/破产申请，已解码)。</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="inlineStr">
+        <is>
+          <t>BPS 破产面板。</t>
+        </is>
+      </c>
+      <c r="E25" s="6" t="inlineStr">
+        <is>
+          <t>L4→MySQL 落库对接（L5）：BPS 破产面板数据源（1 行/破产申请，已解码）。</t>
+        </is>
+      </c>
+      <c r="F25" s="6" t="inlineStr">
+        <is>
+          <t>见 ⑭；L4 解码后同步覆盖更新。</t>
+        </is>
+      </c>
+      <c r="G25" s="6" t="inlineStr">
+        <is>
+          <t>查 BPS 上某贷款全部破产记录落库值。</t>
+        </is>
+      </c>
+      <c r="H25" s="6" t="inlineStr">
+        <is>
+          <t>1 行/破产申请。</t>
+        </is>
+      </c>
+      <c r="I25" s="6" t="inlineStr">
+        <is>
+          <t>port.basic_data_loan_foreclosure_bankruptcy → bpms.sync_loan_foreclosure_bankruptcy〔asset_managment_config.py:822-843〕</t>
+        </is>
+      </c>
+      <c r="J25" s="6" t="inlineStr">
+        <is>
+          <t>port.basic_data_loan_foreclosure_bankruptcy</t>
+        </is>
+      </c>
+      <c r="K25" s="6" t="inlineStr">
+        <is>
+          <t>→ bpms.biz_data_view_loan_details_foreclosure(视图) → BPS 破产面板</t>
+        </is>
+      </c>
+      <c r="L25" s="6" t="inlineStr">
+        <is>
+          <t>bpms.biz_data_view_loan_details_foreclosure</t>
+        </is>
+      </c>
+      <c r="M25" s="6" t="inlineStr"/>
+    </row>
+    <row r="26" ht="96" customHeight="1">
+      <c r="A26" s="16" t="inlineStr">
+        <is>
           <t>㉔ newrez.portnewrezdatadic</t>
         </is>
       </c>
-      <c r="B25" s="6" t="inlineStr">
+      <c r="B26" s="16" t="inlineStr">
         <is>
           <t>字典（Newrez 解码字典）</t>
         </is>
       </c>
-      <c r="C25" s="6" t="inlineStr">
-        <is>
-          <t>Newrez FCL 解码字典(8 列)——把 LM/BK 等编码(LMDeal/LMProgram/LMStatus/LMDecision/BKStatus 等)映射成业务文案。</t>
-        </is>
-      </c>
-      <c r="D25" s="6" t="inlineStr">
+      <c r="C26" s="16" t="inlineStr">
+        <is>
+          <t>Newrez 解码字典——长表(field_name/code/description，1 行/(field_name,code))，把 LM/BK/FCL 等编码(LMDeal/LMProgram/LMStatus/LMDecision/BorrowerIntention/DenialReason/BKStatus/BKStage/LegalStatus 等)映射成业务文案。⚠️ 实测仅 redshift_prod 有此长表；mysql_prod 的 newrez.newrezdatadic 是另一张宽表(只解码 propertytype/loanpurpose 等 6 类、无 LM/BK)。</t>
+        </is>
+      </c>
+      <c r="D26" s="16" t="inlineStr">
         <is>
           <t>给 LM/BK 等表的编码解码提供查找表。</t>
         </is>
       </c>
-      <c r="E25" s="6" t="inlineStr">
+      <c r="E26" s="16" t="inlineStr">
         <is>
           <t>解码字典维度：被 LM/BK 等表 JOIN，提供编码→业务文案的查找（COALESCE 解码）。</t>
         </is>
       </c>
-      <c r="F25" s="6" t="inlineStr">
+      <c r="F26" s="16" t="inlineStr">
         <is>
           <t>源表存编码省空间，展示需文案；统一一张字典 JOIN 解码(COALESCE(dict_desc, raw_code))。</t>
         </is>
       </c>
-      <c r="G25" s="6" t="inlineStr">
+      <c r="G26" s="16" t="inlineStr">
         <is>
           <t>查某编码的业务含义、核对解码是否正确。</t>
         </is>
       </c>
-      <c r="H25" s="6" t="inlineStr">
+      <c r="H26" s="16" t="inlineStr">
         <is>
           <t>1 行/(field_name, code)。</t>
         </is>
       </c>
-      <c r="I25" s="6" t="inlineStr">
+      <c r="I26" s="16" t="inlineStr">
         <is>
           <t>Servicer(Newrez) 文件(L0) → newrez.portnewrezdatadic</t>
         </is>
       </c>
-      <c r="J25" s="6" t="inlineStr">
+      <c r="J26" s="16" t="inlineStr">
         <is>
           <t>Servicer 文件(S3, L0)</t>
         </is>
       </c>
-      <c r="K25" s="6" t="inlineStr">
+      <c r="K26" s="16" t="inlineStr">
         <is>
           <t>⋈ basic_data_pool_config.py(LM :835-840 / BK :367) → port.basic_data_loan_foreclosure_loss_mitigation / _bankruptcy(解码列) → bpms.sync_loan_foreclosure_loss_mitigation / _bankruptcy → 视图 → BPS</t>
         </is>
       </c>
-      <c r="L25" s="6" t="inlineStr">
+      <c r="L26" s="16" t="inlineStr">
         <is>
           <t>port.basic_data_loan_foreclosure_loss_mitigation、port.basic_data_loan_foreclosure_bankruptcy、bpms.sync_loan_foreclosure_loss_mitigation、bpms.sync_loan_foreclosure_bankruptcy</t>
         </is>
       </c>
-      <c r="M25" s="6" t="inlineStr"/>
-    </row>
-    <row r="26" ht="64" customHeight="1">
-      <c r="A26" s="49" t="inlineStr">
+      <c r="M26" s="16" t="inlineStr"/>
+    </row>
+    <row r="27" ht="64" customHeight="1">
+      <c r="A27" s="49" t="inlineStr">
         <is>
           <t>code 列说明（rule 在 PrefectFlow 代码中的出处）： pool = ETL 建表/SQL 代码 flow/basic_data/basic_data_config/basic_data_pool_config.py（在 Redshift 建 FCL 各表、跑 SQL 规则）； asset = BPS 同步 SQL 代码 flow/bps/bps_config/asset_managment_config.py（把 Redshift 结果同步进 BPS 表）； view = BPS 视图 biz_data_view_loan_details_foreclosure 的定义（SHOW CREATE VIEW）； 冒号后数字 = 该文件的行号（例 pool:273 = 该文件第 273 行；GitLab commit 钉 32a750a3，可点开对应行）。</t>
         </is>
@@ -2576,7 +2647,7 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A26:M26"/>
+    <mergeCell ref="A27:M27"/>
     <mergeCell ref="A1:M1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2647,14 +2718,14 @@
     <row r="7" ht="30" customHeight="1">
       <c r="A7" s="36" t="inlineStr">
         <is>
-          <t>业务目的：标准逾期码的单一来源；喂 portmonthbase 与 FCL 业务族(stage 分组)。</t>
+          <t>业务目的：逾期支线标准逾期码的单一来源；喂 port.portmonthbase 月度（不喂 FCL 分组——见下游说明）。</t>
         </is>
       </c>
     </row>
     <row r="8" ht="45" customHeight="1">
       <c r="A8" s="36" t="inlineStr">
         <is>
-          <t>在 pipeline 中的作用：标准逾期码单一来源（L3）：CASE+days360 把 delq_status 归一为标准 delinq 码，喂 portmonthbase 与 FCL stage 分组。</t>
+          <t>在 pipeline 中的作用：标准逾期码单一来源（L3，逾期支线）：CASE+days360 把 delq_status 归一为标准 delinq 码，喂 port.portmonthbase。</t>
         </is>
       </c>
     </row>
@@ -2686,17 +2757,17 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="90" customHeight="1">
+    <row r="13" ht="140" customHeight="1">
       <c r="A13" s="36" t="inlineStr">
         <is>
-          <t>下游链路：→ { port.portmonthbase / port.basic_data_fcl_related.delq_status / port.fcl_stage_info.group } → BPS。另：旁支 port.basic_data_loan_delinq_clean(含 is_ghost_payoff 等)实测存在，但其生成代码不在 PrefectFlow 仓库(grep 0 命中，开放问题)。</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="30" customHeight="1">
+          <t>下游链路：→ port.portmonthbase → BPS（逾期支线月度路径）。⚠️ 本 L3 清洗层不流向 FCL 分组：⑫ basic_data_fcl_related.delq_status / ⑬ fcl_stage_info.group 由 Newrez 原始表(g.delinquency_status_mba + days360(pmt.nextduedate)) 独立重算同一 CASE+days360 逻辑(CREATE_FCL_RELATE_ATTR pool:1696-1770)，并不读本表(2026-06-15 Code-First 订正)。另：旁支 port.basic_data_loan_delinq_clean(含 is_ghost_payoff 等)实测存在，但其生成代码不在 PrefectFlow 仓库(grep 0 命中，开放问题)。</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="18" customHeight="1">
       <c r="A14" s="36" t="inlineStr">
         <is>
-          <t>全部下游表：port.basic_data_fcl_related、port.fcl_stage_info、port.portmonthbase</t>
+          <t>全部下游表：port.portmonthbase</t>
         </is>
       </c>
     </row>
@@ -2707,10 +2778,10 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="30" customHeight="1">
+    <row r="16" ht="60" customHeight="1">
       <c r="A16" s="36" t="inlineStr">
         <is>
-          <t>备注：旁支 port.basic_data_loan_delinq_clean 生成代码不在仓库（grep 0 命中，开放问题），未列为确定下游。</t>
+          <t>备注：旁支 port.basic_data_loan_delinq_clean 生成代码不在仓库（grep 0 命中，开放问题），未列为确定下游。逾期支线 L3 不喂 ⑫/⑬ 的 FCL 分组（后者独立重算同一逻辑，2026-06-15 Code-First 订正）。</t>
         </is>
       </c>
     </row>
@@ -6668,10 +6739,10 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="30" customHeight="1">
+    <row r="9" ht="140" customHeight="1">
       <c r="A9" s="36" t="inlineStr">
         <is>
-          <t>为什么会有这张表：UNION 前必须先统一列名；单列一张临时表做改名，逻辑清晰、便于调试；运行时产物。</t>
+          <t>为什么会有这张表：为什么单列这张临时表、而非直接生成 ⑩：它是【单消费者暂存表】(仅被 ⑩ 读，pool:1686)，物化它是工程权衡而非复用——①关注点分离：⑨ 专做‘三家 servicer 异构源 UNION + 列名归一化’(pool:1532-1654)，⑩ 只做‘LEFT JOIN Hold 历史’(pool:1657-1692)；②可读：单 UNION 约 120 行，内联进 ⑩ 的 join 会变成约 150 行嵌套大查询；③Redshift 性能：先把 UNION 物化成带统计信息的实体表再 join，比‘join 里塞三路 UNION 子查询’计划更稳、更快；④可调试：可直接查暂存表看‘UNION 完、挂 Hold 前’的中间态。属标准 ETL staging、非缺陷；理论上可用 CTE/真 TEMP 表省一次落盘，但当前复杂度下拆两步更优。</t>
         </is>
       </c>
     </row>
@@ -13092,7 +13163,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G31"/>
+  <dimension ref="A1:G32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -13154,17 +13225,17 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="45" customHeight="1">
+    <row r="8" ht="60" customHeight="1">
       <c r="A8" s="36" t="inlineStr">
         <is>
-          <t>在 pipeline 中的作用：分组键提供者（L4）：合并逾期码与 FCL 属性，为 stage 计算提供分组键（delq_status→group）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="30" customHeight="1">
+          <t>在 pipeline 中的作用：分组键提供者（L4）：把 5 张 Newrez 原始表(general/liq/pmt/bk/prop)+ Carrington 源的关联属性合并，为 stage 计算提供分组键（delq_status→group）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="135" customHeight="1">
       <c r="A9" s="36" t="inlineStr">
         <is>
-          <t>为什么会有这张表：stage 计算需把逾期支线的 delq_status 与 FCL 属性合并；单列一张关联表承接，避免主时间线表过宽。</t>
+          <t>为什么会有这张表：把 5 张 Newrez 原始表(general/liq/pmt/bk/prop)与 Carrington 源(portcarrington)的【诉讼/清算/BK/违约/逾期分类】按 loanid+dataasof 合并成一张窄关联表(1 行/贷款)，供 ⑬ stage 计算取 delq_status 作分组键(group)；单列一张承接，避免主时间线表过宽。注：delq_status 由 g.delinquency_status_mba + days360(pmt.nextduedate, dataasof) 现算，并非取自逾期支线 daily_loan_common_clean。</t>
         </is>
       </c>
     </row>
@@ -13175,17 +13246,17 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="75" customHeight="1">
+    <row r="11" ht="135" customHeight="1">
       <c r="A11" s="36" t="inlineStr">
         <is>
-          <t>上游链路：{ port.basic_data_loan_fcl(FCL 属性) + port.basic_data_daily_loan_common_clean.delinq(逾期码) } → port.basic_data_fcl_related〔basic_data_pool_config.py〕</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="30" customHeight="1">
+          <t>上游链路：{ newrez.portnewrezgeneral(g) + newrez.portnewrezliq(l) + newrez.portnewrezpmt(pmt) + newrez.portnewrezbk(bk) + newrez.portnewrezprop(pr)，按 loanid+dataasof JOIN }〔Newrez 分支〕 UNION { carrington.portcarrington(c) }〔Carrington 分支〕 → port.basic_data_fcl_related〔CREATE_FCL_RELATE_ATTR basic_data_pool_config.py:1696-1770〕</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="60" customHeight="1">
       <c r="A12" s="36" t="inlineStr">
         <is>
-          <t>全部上游表：port.basic_data_loan_fcl、port.basic_data_daily_loan_common_clean</t>
+          <t>全部上游表：newrez.portnewrezgeneral、newrez.portnewrezliq、newrez.portnewrezpmt、newrez.portnewrezbk、newrez.portnewrezprop、carrington.portcarrington</t>
         </is>
       </c>
     </row>
@@ -13210,304 +13281,274 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="18" customHeight="1">
-      <c r="A16" s="37" t="inlineStr">
+    <row r="16" ht="140" customHeight="1">
+      <c r="A16" s="36" t="inlineStr">
+        <is>
+          <t>备注：上游为 5 张 Newrez 原始表(general/liq/pmt/bk/prop) + carrington.portcarrington（代码 CREATE_FCL_RELATE_ATTR pool:1696-1770 实测，按 loanid+dataasof JOIN 后 UNION）；并非 basic_data_loan_fcl / daily_loan_common_clean（旧元数据误标，2026-06-15 经 Code-First 订正）。SQL 表别名：g=portnewrezgeneral、l=portnewrezliq、pmt=portnewrezpmt、bk=portnewrezbk、pr=portnewrezprop、c=portcarrington。</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="18" customHeight="1">
+      <c r="A17" s="37" t="inlineStr">
         <is>
           <t>▲ 以上为「业务含义与全链路血缘」说明块；下方为原始数据 ────</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="8" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="8" t="inlineStr">
         <is>
           <t>字段</t>
         </is>
       </c>
-      <c r="B17" s="8" t="inlineStr">
+      <c r="B18" s="8" t="inlineStr">
         <is>
           <t>业务含义</t>
         </is>
       </c>
-      <c r="C17" s="8" t="inlineStr">
+      <c r="C18" s="8" t="inlineStr">
         <is>
           <t>7727000088</t>
         </is>
       </c>
-      <c r="D17" s="8" t="inlineStr">
+      <c r="D18" s="8" t="inlineStr">
         <is>
           <t>7727000672</t>
         </is>
       </c>
-      <c r="E17" s="8" t="inlineStr">
+      <c r="E18" s="8" t="inlineStr">
         <is>
           <t>7727004200</t>
         </is>
       </c>
-      <c r="F17" s="8" t="inlineStr">
+      <c r="F18" s="8" t="inlineStr">
         <is>
           <t>7727000065</t>
         </is>
       </c>
-      <c r="G17" s="8" t="inlineStr">
+      <c r="G18" s="8" t="inlineStr">
         <is>
           <t>7727000010</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="15" t="inlineStr">
-        <is>
-          <t>dataasof</t>
-        </is>
-      </c>
-      <c r="B18" s="15" t="inlineStr">
-        <is>
-          <t>数据快照日期</t>
-        </is>
-      </c>
-      <c r="C18" s="6" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="D18" s="6" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="E18" s="6" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="F18" s="6" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="G18" s="6" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="15" t="inlineStr">
         <is>
-          <t>loanid</t>
+          <t>dataasof</t>
         </is>
       </c>
       <c r="B19" s="15" t="inlineStr">
         <is>
-          <t>投资人贷款ID（跨 Servicer 的统一标识）</t>
-        </is>
-      </c>
-      <c r="C19" s="16" t="inlineStr">
-        <is>
-          <t>7727000088</t>
-        </is>
-      </c>
-      <c r="D19" s="16" t="inlineStr">
-        <is>
-          <t>7727000672</t>
-        </is>
-      </c>
-      <c r="E19" s="16" t="inlineStr">
-        <is>
-          <t>7727004200</t>
-        </is>
-      </c>
-      <c r="F19" s="16" t="inlineStr">
-        <is>
-          <t>7727000065</t>
-        </is>
-      </c>
-      <c r="G19" s="16" t="inlineStr">
-        <is>
-          <t>7727000010</t>
+          <t>数据快照日期</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="E19" s="6" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="F19" s="6" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="G19" s="6" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="15" t="inlineStr">
         <is>
-          <t>servicer</t>
+          <t>loanid</t>
         </is>
       </c>
       <c r="B20" s="15" t="inlineStr">
         <is>
-          <t>当前服务商名称（hardcoded）</t>
-        </is>
-      </c>
-      <c r="C20" s="6" t="inlineStr">
-        <is>
-          <t>Newrez</t>
-        </is>
-      </c>
-      <c r="D20" s="6" t="inlineStr">
-        <is>
-          <t>Newrez</t>
-        </is>
-      </c>
-      <c r="E20" s="6" t="inlineStr">
-        <is>
-          <t>Newrez</t>
-        </is>
-      </c>
-      <c r="F20" s="6" t="inlineStr">
-        <is>
-          <t>Newrez</t>
-        </is>
-      </c>
-      <c r="G20" s="6" t="inlineStr">
-        <is>
-          <t>Newrez</t>
+          <t>投资人贷款ID（跨 Servicer 的统一标识）</t>
+        </is>
+      </c>
+      <c r="C20" s="16" t="inlineStr">
+        <is>
+          <t>7727000088</t>
+        </is>
+      </c>
+      <c r="D20" s="16" t="inlineStr">
+        <is>
+          <t>7727000672</t>
+        </is>
+      </c>
+      <c r="E20" s="16" t="inlineStr">
+        <is>
+          <t>7727004200</t>
+        </is>
+      </c>
+      <c r="F20" s="16" t="inlineStr">
+        <is>
+          <t>7727000065</t>
+        </is>
+      </c>
+      <c r="G20" s="16" t="inlineStr">
+        <is>
+          <t>7727000010</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="15" t="inlineStr">
         <is>
-          <t>delq_status</t>
+          <t>servicer</t>
         </is>
       </c>
       <c r="B21" s="15" t="inlineStr">
         <is>
-          <t>Servicer 原始逾期状态描述（未标准化）</t>
-        </is>
-      </c>
-      <c r="C21" s="16" t="inlineStr">
-        <is>
-          <t>REO</t>
-        </is>
-      </c>
-      <c r="D21" s="16" t="inlineStr">
-        <is>
-          <t>D120P</t>
-        </is>
-      </c>
-      <c r="E21" s="16" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="F21" s="16" t="inlineStr">
-        <is>
-          <t>REO</t>
-        </is>
-      </c>
-      <c r="G21" s="16" t="inlineStr">
-        <is>
-          <t>D60</t>
+          <t>当前服务商名称（hardcoded）</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>Newrez</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>Newrez</t>
+        </is>
+      </c>
+      <c r="E21" s="6" t="inlineStr">
+        <is>
+          <t>Newrez</t>
+        </is>
+      </c>
+      <c r="F21" s="6" t="inlineStr">
+        <is>
+          <t>Newrez</t>
+        </is>
+      </c>
+      <c r="G21" s="6" t="inlineStr">
+        <is>
+          <t>Newrez</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="15" t="inlineStr">
         <is>
-          <t>isloanlitigated</t>
+          <t>delq_status</t>
         </is>
       </c>
       <c r="B22" s="15" t="inlineStr">
         <is>
-          <t>贷款是否处于诉讼中（0/1）</t>
-        </is>
-      </c>
-      <c r="C22" s="6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D22" s="6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E22" s="6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F22" s="6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G22" s="6" t="inlineStr">
-        <is>
-          <t>0</t>
+          <t>Servicer 原始逾期状态描述（未标准化）</t>
+        </is>
+      </c>
+      <c r="C22" s="16" t="inlineStr">
+        <is>
+          <t>REO</t>
+        </is>
+      </c>
+      <c r="D22" s="16" t="inlineStr">
+        <is>
+          <t>D120P</t>
+        </is>
+      </c>
+      <c r="E22" s="16" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="F22" s="16" t="inlineStr">
+        <is>
+          <t>REO</t>
+        </is>
+      </c>
+      <c r="G22" s="16" t="inlineStr">
+        <is>
+          <t>D60</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="15" t="inlineStr">
         <is>
-          <t>deactreason</t>
+          <t>isloanlitigated</t>
         </is>
       </c>
       <c r="B23" s="15" t="inlineStr">
         <is>
-          <t>停用/退出原因（如 FC-BK）</t>
-        </is>
-      </c>
-      <c r="C23" s="16" t="inlineStr">
-        <is>
-          <t>FC-BK</t>
-        </is>
-      </c>
-      <c r="D23" s="16" t="inlineStr">
-        <is>
-          <t>FC-BK</t>
-        </is>
-      </c>
-      <c r="E23" s="16" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F23" s="16" t="inlineStr">
-        <is>
-          <t>FC-BK</t>
-        </is>
-      </c>
-      <c r="G23" s="16" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>贷款是否处于诉讼中（0/1）</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E23" s="6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F23" s="6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G23" s="6" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="15" t="inlineStr">
         <is>
-          <t>reasonfordefault</t>
+          <t>deactreason</t>
         </is>
       </c>
       <c r="B24" s="15" t="inlineStr">
         <is>
-          <t>借款人违约原因描述</t>
-        </is>
-      </c>
-      <c r="C24" s="6" t="inlineStr">
-        <is>
-          <t>Reduction in Borrower's Income</t>
-        </is>
-      </c>
-      <c r="D24" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E24" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F24" s="6" t="inlineStr">
-        <is>
-          <t>Unable to Contact Borrower</t>
-        </is>
-      </c>
-      <c r="G24" s="6" t="inlineStr">
+          <t>停用/退出原因（如 FC-BK）</t>
+        </is>
+      </c>
+      <c r="C24" s="16" t="inlineStr">
+        <is>
+          <t>FC-BK</t>
+        </is>
+      </c>
+      <c r="D24" s="16" t="inlineStr">
+        <is>
+          <t>FC-BK</t>
+        </is>
+      </c>
+      <c r="E24" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F24" s="16" t="inlineStr">
+        <is>
+          <t>FC-BK</t>
+        </is>
+      </c>
+      <c r="G24" s="16" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -13516,109 +13557,109 @@
     <row r="25">
       <c r="A25" s="15" t="inlineStr">
         <is>
-          <t>inauctionflag</t>
+          <t>reasonfordefault</t>
         </is>
       </c>
       <c r="B25" s="15" t="inlineStr">
         <is>
-          <t>是否在拍卖中（0/1）</t>
-        </is>
-      </c>
-      <c r="C25" s="16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D25" s="16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E25" s="16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F25" s="16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G25" s="16" t="inlineStr">
-        <is>
-          <t>0</t>
+          <t>借款人违约原因描述</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t>Reduction in Borrower's Income</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E25" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F25" s="6" t="inlineStr">
+        <is>
+          <t>Unable to Contact Borrower</t>
+        </is>
+      </c>
+      <c r="G25" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="15" t="inlineStr">
         <is>
-          <t>liquidationdate</t>
+          <t>inauctionflag</t>
         </is>
       </c>
       <c r="B26" s="15" t="inlineStr">
         <is>
-          <t>清算/处置日</t>
-        </is>
-      </c>
-      <c r="C26" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D26" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E26" s="6" t="inlineStr">
-        <is>
-          <t>2026-04-16</t>
-        </is>
-      </c>
-      <c r="F26" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G26" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>是否在拍卖中（0/1）</t>
+        </is>
+      </c>
+      <c r="C26" s="16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D26" s="16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E26" s="16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F26" s="16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G26" s="16" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="15" t="inlineStr">
         <is>
-          <t>liquidationtype</t>
+          <t>liquidationdate</t>
         </is>
       </c>
       <c r="B27" s="15" t="inlineStr">
         <is>
-          <t>清算/处置类型</t>
-        </is>
-      </c>
-      <c r="C27" s="16" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D27" s="16" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E27" s="16" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
-      </c>
-      <c r="F27" s="16" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G27" s="16" t="inlineStr">
+          <t>清算/处置日</t>
+        </is>
+      </c>
+      <c r="C27" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D27" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E27" s="6" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="F27" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G27" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -13627,35 +13668,35 @@
     <row r="28">
       <c r="A28" s="15" t="inlineStr">
         <is>
-          <t>liquidationproceeds</t>
+          <t>liquidationtype</t>
         </is>
       </c>
       <c r="B28" s="15" t="inlineStr">
         <is>
-          <t>清算/处置回收款</t>
-        </is>
-      </c>
-      <c r="C28" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D28" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E28" s="6" t="inlineStr">
-        <is>
-          <t>503557.98</t>
-        </is>
-      </c>
-      <c r="F28" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G28" s="6" t="inlineStr">
+          <t>清算/处置类型</t>
+        </is>
+      </c>
+      <c r="C28" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D28" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E28" s="16" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="F28" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G28" s="16" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -13664,132 +13705,170 @@
     <row r="29">
       <c r="A29" s="15" t="inlineStr">
         <is>
-          <t>pmt</t>
+          <t>liquidationproceeds</t>
         </is>
       </c>
       <c r="B29" s="15" t="inlineStr">
         <is>
-          <t>月供</t>
-        </is>
-      </c>
-      <c r="C29" s="16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D29" s="16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E29" s="16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F29" s="16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G29" s="16" t="inlineStr">
-        <is>
-          <t>6339.72</t>
+          <t>清算/处置回收款</t>
+        </is>
+      </c>
+      <c r="C29" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D29" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E29" s="6" t="inlineStr">
+        <is>
+          <t>503557.98</t>
+        </is>
+      </c>
+      <c r="F29" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G29" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="15" t="inlineStr">
         <is>
-          <t>bk_flag</t>
+          <t>pmt</t>
         </is>
       </c>
       <c r="B30" s="15" t="inlineStr">
         <is>
-          <t>是否破产标记（0/1）</t>
-        </is>
-      </c>
-      <c r="C30" s="6" t="inlineStr">
+          <t>月供</t>
+        </is>
+      </c>
+      <c r="C30" s="16" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D30" s="6" t="inlineStr">
+      <c r="D30" s="16" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E30" s="6" t="inlineStr">
+      <c r="E30" s="16" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F30" s="6" t="inlineStr">
+      <c r="F30" s="16" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G30" s="6" t="inlineStr">
-        <is>
-          <t>1</t>
+      <c r="G30" s="16" t="inlineStr">
+        <is>
+          <t>6339.72</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="15" t="inlineStr">
         <is>
+          <t>bk_flag</t>
+        </is>
+      </c>
+      <c r="B31" s="15" t="inlineStr">
+        <is>
+          <t>是否破产标记（0/1）</t>
+        </is>
+      </c>
+      <c r="C31" s="6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D31" s="6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E31" s="6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F31" s="6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G31" s="6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="15" t="inlineStr">
+        <is>
           <t>propertystate</t>
         </is>
       </c>
-      <c r="B31" s="15" t="inlineStr">
+      <c r="B32" s="15" t="inlineStr">
         <is>
           <t>房产所在州（决定司法/非司法法拍路径）</t>
         </is>
       </c>
-      <c r="C31" s="16" t="inlineStr">
+      <c r="C32" s="16" t="inlineStr">
         <is>
           <t>FL</t>
         </is>
       </c>
-      <c r="D31" s="16" t="inlineStr">
+      <c r="D32" s="16" t="inlineStr">
         <is>
           <t>MI</t>
         </is>
       </c>
-      <c r="E31" s="16" t="inlineStr">
+      <c r="E32" s="16" t="inlineStr">
         <is>
           <t>IL</t>
         </is>
       </c>
-      <c r="F31" s="16" t="inlineStr">
+      <c r="F32" s="16" t="inlineStr">
         <is>
           <t>FL</t>
         </is>
       </c>
-      <c r="G31" s="16" t="inlineStr">
+      <c r="G32" s="16" t="inlineStr">
         <is>
           <t>FL</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="16">
-    <mergeCell ref="A13:G13"/>
+  <mergeCells count="17">
     <mergeCell ref="A14:G14"/>
     <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A17:G17"/>
+    <mergeCell ref="A8:G8"/>
+    <mergeCell ref="A6:G6"/>
+    <mergeCell ref="A4:G4"/>
+    <mergeCell ref="A16:G16"/>
+    <mergeCell ref="A7:G7"/>
+    <mergeCell ref="A10:G10"/>
+    <mergeCell ref="A13:G13"/>
     <mergeCell ref="A9:G9"/>
-    <mergeCell ref="A8:G8"/>
     <mergeCell ref="A3:G3"/>
-    <mergeCell ref="A6:G6"/>
-    <mergeCell ref="A5:G5"/>
-    <mergeCell ref="A4:G4"/>
     <mergeCell ref="A12:G12"/>
     <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A16:G16"/>
     <mergeCell ref="A15:G15"/>
-    <mergeCell ref="A7:G7"/>
     <mergeCell ref="A11:G11"/>
-    <mergeCell ref="A10:G10"/>
+    <mergeCell ref="A5:G5"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -13884,17 +13963,17 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="75" customHeight="1">
+    <row r="11" ht="120" customHeight="1">
       <c r="A11" s="36" t="inlineStr">
         <is>
-          <t>上游链路：{ port.basic_data_loan_fcl + port.basic_data_fcl_related(delq_status 分组) + port.portfunding(JOIN) } → port.fcl_stage_info〔GEN_FCL_STAGE basic_data_pool_config.py:1774-2440〕</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="60" customHeight="1">
+          <t>上游链路：{ port.basic_data_loan_fcl + port.basic_data_fcl_related(delq_status 分组) + port.basic_data_loan_foreclosure_loss_mitigation + port.basic_data_loan_foreclosure_hold(算 in_lm/on_hold) + port.portfunding(JOIN) } → port.fcl_stage_info〔GEN_FCL_STAGE basic_data_pool_config.py:1774-2440〕</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="75" customHeight="1">
       <c r="A12" s="36" t="inlineStr">
         <is>
-          <t>全部上游表：port.basic_data_loan_fcl、port.basic_data_fcl_related、port.basic_data_daily_loan_common_clean、port.portfunding</t>
+          <t>全部上游表：port.basic_data_loan_fcl、port.basic_data_fcl_related、port.basic_data_loan_foreclosure_loss_mitigation、port.basic_data_loan_foreclosure_hold、port.portfunding</t>
         </is>
       </c>
     </row>
@@ -40646,10 +40725,10 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="45" customHeight="1">
+    <row r="6" ht="135" customHeight="1">
       <c r="A6" s="36" t="inlineStr">
         <is>
-          <t>业务说明：Newrez FCL 解码字典(8 列)——把 LM/BK 等编码(LMDeal/LMProgram/LMStatus/LMDecision/BKStatus 等)映射成业务文案。</t>
+          <t>业务说明：Newrez 解码字典——长表(field_name/code/description，1 行/(field_name,code))，把 LM/BK/FCL 等编码(LMDeal/LMProgram/LMStatus/LMDecision/BorrowerIntention/DenialReason/BKStatus/BKStage/LegalStatus 等)映射成业务文案。⚠️ 实测仅 redshift_prod 有此长表；mysql_prod 的 newrez.newrezdatadic 是另一张宽表(只解码 propertytype/loanpurpose 等 6 类、无 LM/BK)。</t>
         </is>
       </c>
     </row>
@@ -45703,17 +45782,17 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="120" customHeight="1">
+    <row r="13" ht="140" customHeight="1">
       <c r="A13" s="36" t="inlineStr">
         <is>
-          <t>下游链路：portnewrezbk → port.basic_data_loan_foreclosure_bankruptcy〔解码 bkstatus，basic_data_pool_config.py:331-370，JOIN newrez.portnewrezdatadic〕 → bpms.sync_loan_foreclosure_bankruptcy〔asset_managment_config.py:822-843〕 → bpms.biz_data_view_loan_details_foreclosure(视图) → BPS 破产面板</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="60" customHeight="1">
+          <t>下游链路：portnewrezbk → port.basic_data_loan_foreclosure_bankruptcy〔解码 bkstatus，basic_data_pool_config.py:331-370，JOIN newrez.portnewrezdatadic〕 → bpms.sync_loan_foreclosure_bankruptcy〔asset_managment_config.py:822-843〕 → bpms.biz_data_view_loan_details_foreclosure(视图) → BPS 破产面板。另：bk.activebkflag → port.basic_data_fcl_related.bk_flag(⑫，CREATE_FCL_RELATE_ATTR pool:1720)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="75" customHeight="1">
       <c r="A14" s="36" t="inlineStr">
         <is>
-          <t>全部下游表：port.basic_data_loan_foreclosure_bankruptcy、bpms.sync_loan_foreclosure_bankruptcy、bpms.biz_data_view_loan_details_foreclosure</t>
+          <t>全部下游表：port.basic_data_loan_foreclosure_bankruptcy、port.basic_data_fcl_related、bpms.sync_loan_foreclosure_bankruptcy、bpms.biz_data_view_loan_details_foreclosure</t>
         </is>
       </c>
     </row>
@@ -50380,7 +50459,7 @@
     <row r="13" ht="140" customHeight="1">
       <c r="A13" s="36" t="inlineStr">
         <is>
-          <t>下游链路：portnewrezgeneral.delinquency_status_mba → port.portdaily_v2〔portdaily_config.py〕 → port.basic_data_daily_loan_common.delq_status(逾期支线 L2，daily_data_loan_common_config.py) → port.basic_data_daily_loan_common_clean.delinq(L3，daily_data_loan_common_clean_config.py，CASE+days360) → { port.basic_data_fcl_related.delq_status / port.fcl_stage_info.group / port.portmonthbase } → BPS</t>
+          <t>下游链路：portnewrezgeneral.delinquency_status_mba 有两条独立去向：(A 逾期支线) → port.portdaily_v2 → port.basic_data_daily_loan_common.delq_status(L2) → port.basic_data_daily_loan_common_clean.delinq(L3，CASE+days360) → port.portmonthbase → BPS；(B FCL 分组) general 被 CREATE_FCL_RELATE_ATTR(pool:1696-1770) 直接读取 → port.basic_data_fcl_related.delq_status → port.fcl_stage_info.group → bpms.sync_fcl_stage_info → BPS。⚠️ B 路不经 daily_loan_common_clean——⑫ 用同一 CASE+days360 逻辑独立重算。</t>
         </is>
       </c>
     </row>
@@ -55193,17 +55272,17 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="75" customHeight="1">
+    <row r="13" ht="120" customHeight="1">
       <c r="A13" s="36" t="inlineStr">
         <is>
-          <t>下游链路：portnewrezprop.propertystate → port.basic_data_daily_loan_common(州维度) / port.basic_data_loan_foreclosure(summary_judicial_foreclosure 司法标志) → bpms.sync_loan_foreclosure → BPS</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="45" customHeight="1">
+          <t>下游链路：portnewrezprop.propertystate → port.basic_data_daily_loan_common(州维度) / port.basic_data_loan_foreclosure(summary_judicial_foreclosure 司法标志) → bpms.sync_loan_foreclosure → BPS。另：pr.propertystate → port.basic_data_fcl_related.propertystate(⑫，CREATE_FCL_RELATE_ATTR pool:1721)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="60" customHeight="1">
       <c r="A14" s="36" t="inlineStr">
         <is>
-          <t>全部下游表：port.basic_data_daily_loan_common、port.basic_data_loan_foreclosure、bpms.sync_loan_foreclosure</t>
+          <t>全部下游表：port.basic_data_daily_loan_common、port.basic_data_loan_foreclosure、port.basic_data_fcl_related、bpms.sync_loan_foreclosure</t>
         </is>
       </c>
     </row>
@@ -56568,17 +56647,17 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="60" customHeight="1">
+    <row r="13" ht="120" customHeight="1">
       <c r="A13" s="36" t="inlineStr">
         <is>
-          <t>下游链路：→ port.basic_data_daily_loan_common_clean(L3) → { port.portmonthbase / port.basic_data_fcl_related.delq_status / port.fcl_stage_info.group } → BPS</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="45" customHeight="1">
+          <t>下游链路：→ port.basic_data_daily_loan_common_clean(L3) → port.portmonthbase → BPS（逾期支线月度路径）。注：FCL 分组 fcl_stage_info.group / ⑫ basic_data_fcl_related.delq_status 不经本表——⑫ 由 Newrez 原始表(g.delinquency_status_mba + days360(pmt.nextduedate)) 独立重算同一逻辑，见 CREATE_FCL_RELATE_ATTR pool:1696-1770。</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="30" customHeight="1">
       <c r="A14" s="36" t="inlineStr">
         <is>
-          <t>全部下游表：port.basic_data_daily_loan_common_clean、port.basic_data_fcl_related、port.fcl_stage_info、port.portmonthbase</t>
+          <t>全部下游表：port.basic_data_daily_loan_common_clean、port.portmonthbase</t>
         </is>
       </c>
     </row>
@@ -56589,10 +56668,10 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="30" customHeight="1">
+    <row r="16" ht="60" customHeight="1">
       <c r="A16" s="36" t="inlineStr">
         <is>
-          <t>备注：fcl_flag 在 L2 未归一（直传，Newrez/SLS NULL）；真正归一在 L4 FCL 业务族。</t>
+          <t>备注：fcl_flag 在 L2 未归一（直传，Newrez/SLS NULL）；真正归一在 L4 FCL 业务族。逾期支线(本表/⑧)只流向 portmonthbase 月度，不流向 ⑫/⑬ 的 FCL 分组（后者独立重算，2026-06-15 Code-First 订正）。</t>
         </is>
       </c>
     </row>
